--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="469" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="137">
   <si>
     <t>group</t>
   </si>
@@ -132,289 +132,262 @@
     <t>0.027</t>
   </si>
   <si>
-    <t>HT4_HT6_Int</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + 5-HT4x5-HT6</t>
+    <t>HT4_HT6_ROEint</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
+  </si>
+  <si>
+    <t>0.836</t>
+  </si>
+  <si>
+    <t>0.059</t>
+  </si>
+  <si>
+    <t>0.653</t>
+  </si>
+  <si>
+    <t>R_5HT4_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT4 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.306</t>
+  </si>
+  <si>
+    <t>R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.004</t>
+  </si>
+  <si>
+    <t>HT4_HT6_ROEint_Cov</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.155</t>
+  </si>
+  <si>
+    <t>0.013</t>
+  </si>
+  <si>
+    <t>0.391</t>
+  </si>
+  <si>
+    <t>0.008</t>
+  </si>
+  <si>
+    <t>0.208</t>
+  </si>
+  <si>
+    <t>0.005</t>
+  </si>
+  <si>
+    <t>sex_female</t>
+  </si>
+  <si>
+    <t>Sex (female)</t>
+  </si>
+  <si>
+    <t>0.628</t>
+  </si>
+  <si>
+    <t>log_MME</t>
+  </si>
+  <si>
+    <t>log10 MME</t>
+  </si>
+  <si>
+    <t>0.433</t>
+  </si>
+  <si>
+    <t>MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>Tramadol group</t>
+  </si>
+  <si>
+    <t>0.633</t>
+  </si>
+  <si>
+    <t>0.365</t>
+  </si>
+  <si>
+    <t>0.482</t>
+  </si>
+  <si>
+    <t>0.388</t>
+  </si>
+  <si>
+    <t>0.154</t>
+  </si>
+  <si>
+    <t>0.093</t>
+  </si>
+  <si>
+    <t>0.442</t>
+  </si>
+  <si>
+    <t>0.142</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>0.610</t>
+  </si>
+  <si>
+    <t>0.847</t>
+  </si>
+  <si>
+    <t>0.321</t>
+  </si>
+  <si>
+    <t>0.413</t>
+  </si>
+  <si>
+    <t>0.346</t>
+  </si>
+  <si>
+    <t>0.489</t>
+  </si>
+  <si>
+    <t>0.458</t>
+  </si>
+  <si>
+    <t>0.529</t>
+  </si>
+  <si>
+    <t>0.410</t>
+  </si>
+  <si>
+    <t>0.310</t>
+  </si>
+  <si>
+    <t>0.438</t>
+  </si>
+  <si>
+    <t>0.349</t>
+  </si>
+  <si>
+    <t>0.680</t>
+  </si>
+  <si>
+    <t>0.892</t>
+  </si>
+  <si>
+    <t>0.361</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>adj_R2</t>
+  </si>
+  <si>
+    <t>F_stat</t>
+  </si>
+  <si>
+    <t>df1</t>
+  </si>
+  <si>
+    <t>df2</t>
+  </si>
+  <si>
+    <t>F_p</t>
+  </si>
+  <si>
+    <t>sigma</t>
+  </si>
+  <si>
+    <t>RMSE</t>
+  </si>
+  <si>
+    <t>AIC</t>
+  </si>
+  <si>
+    <t>BIC</t>
+  </si>
+  <si>
+    <t>max_VIF</t>
+  </si>
+  <si>
+    <t>max_cooksD</t>
+  </si>
+  <si>
+    <t>shapiro_p</t>
+  </si>
+  <si>
+    <t>bp_p</t>
+  </si>
+  <si>
+    <t>F_p_fmt</t>
+  </si>
+  <si>
+    <t>SOWS ~ log_ROE + R_5HT4</t>
   </si>
   <si>
     <t>0.129</t>
   </si>
   <si>
-    <t>0.971</t>
-  </si>
-  <si>
-    <t>0.017</t>
-  </si>
-  <si>
-    <t>0.006</t>
-  </si>
-  <si>
-    <t>R_5HT4_x_5HT6</t>
-  </si>
-  <si>
-    <t>5-HT4 x 5-HT6</t>
-  </si>
-  <si>
-    <t>0.025</t>
-  </si>
-  <si>
-    <t>HT4_HT6_Cov</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + Sex + MQS non-opioid + log MME + DOU</t>
-  </si>
-  <si>
-    <t>0.491</t>
-  </si>
-  <si>
-    <t>0.283</t>
-  </si>
-  <si>
-    <t>0.304</t>
-  </si>
-  <si>
-    <t>0.285</t>
-  </si>
-  <si>
-    <t>sex_female</t>
-  </si>
-  <si>
-    <t>Sex (female)</t>
-  </si>
-  <si>
-    <t>0.269</t>
-  </si>
-  <si>
-    <t>MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>MQS non-opioid</t>
-  </si>
-  <si>
-    <t>0.848</t>
-  </si>
-  <si>
-    <t>log_MME</t>
-  </si>
-  <si>
-    <t>log10 MME</t>
-  </si>
-  <si>
-    <t>0.134</t>
-  </si>
-  <si>
-    <t>DOU</t>
-  </si>
-  <si>
-    <t>DOU (yr)</t>
-  </si>
-  <si>
-    <t>0.475</t>
-  </si>
-  <si>
-    <t>HT4_HT6_Cov_noMME</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + Sex + MQS non-opioid + DOU</t>
-  </si>
-  <si>
-    <t>0.778</t>
-  </si>
-  <si>
-    <t>0.143</t>
-  </si>
-  <si>
-    <t>0.090</t>
-  </si>
-  <si>
-    <t>0.082</t>
-  </si>
-  <si>
-    <t>0.564</t>
-  </si>
-  <si>
-    <t>0.721</t>
-  </si>
-  <si>
-    <t>Tramadol group</t>
-  </si>
-  <si>
-    <t>0.633</t>
-  </si>
-  <si>
-    <t>0.365</t>
-  </si>
-  <si>
-    <t>0.482</t>
-  </si>
-  <si>
-    <t>0.388</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>0.442</t>
-  </si>
-  <si>
-    <t>0.142</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>0.620</t>
-  </si>
-  <si>
-    <t>0.206</t>
+    <t>SOWS ~ log_ROE + R_5HT6</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6</t>
+  </si>
+  <si>
+    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE +      sex_female + log_MME + MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>0.003</t>
+  </si>
+  <si>
+    <t>0.467</t>
   </si>
   <si>
     <t>0.140</t>
   </si>
   <si>
-    <t>0.029</t>
-  </si>
-  <si>
-    <t>0.508</t>
-  </si>
-  <si>
-    <t>0.640</t>
-  </si>
-  <si>
-    <t>0.401</t>
-  </si>
-  <si>
-    <t>0.036</t>
-  </si>
-  <si>
-    <t>0.682</t>
-  </si>
-  <si>
-    <t>0.647</t>
-  </si>
-  <si>
-    <t>0.658</t>
-  </si>
-  <si>
-    <t>0.683</t>
-  </si>
-  <si>
-    <t>0.245</t>
-  </si>
-  <si>
-    <t>0.071</t>
-  </si>
-  <si>
-    <t>0.039</t>
-  </si>
-  <si>
-    <t>0.553</t>
-  </si>
-  <si>
-    <t>0.651</t>
-  </si>
-  <si>
-    <t>0.634</t>
-  </si>
-  <si>
-    <t>formula</t>
-  </si>
-  <si>
-    <t>n</t>
-  </si>
-  <si>
-    <t>k</t>
-  </si>
-  <si>
-    <t>R2</t>
-  </si>
-  <si>
-    <t>adj_R2</t>
-  </si>
-  <si>
-    <t>F_stat</t>
-  </si>
-  <si>
-    <t>df1</t>
-  </si>
-  <si>
-    <t>df2</t>
-  </si>
-  <si>
-    <t>F_p</t>
-  </si>
-  <si>
-    <t>sigma</t>
-  </si>
-  <si>
-    <t>RMSE</t>
-  </si>
-  <si>
-    <t>AIC</t>
-  </si>
-  <si>
-    <t>BIC</t>
-  </si>
-  <si>
-    <t>max_VIF</t>
-  </si>
-  <si>
-    <t>max_cooksD</t>
-  </si>
-  <si>
-    <t>shapiro_p</t>
-  </si>
-  <si>
-    <t>bp_p</t>
-  </si>
-  <si>
-    <t>F_p_fmt</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT4</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT6</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_5HT6</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid +      log_MME + DOU</t>
-  </si>
-  <si>
-    <t>0.066</t>
-  </si>
-  <si>
-    <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid +      DOU</t>
-  </si>
-  <si>
-    <t>0.055</t>
-  </si>
-  <si>
-    <t>0.467</t>
-  </si>
-  <si>
     <t>0.072</t>
   </si>
   <si>
-    <t>0.125</t>
-  </si>
-  <si>
-    <t>0.244</t>
-  </si>
-  <si>
-    <t>0.251</t>
+    <t>0.188</t>
+  </si>
+  <si>
+    <t>0.300</t>
   </si>
   <si>
     <t>setting</t>
@@ -441,7 +414,7 @@
     <t>models</t>
   </si>
   <si>
-    <t>HT4: SOWS ~ log_ROE + R_5HT4  |  HT6: SOWS ~ log_ROE + R_5HT6  |  HT4_HT6: SOWS ~ log_ROE + R_5HT4 + R_5HT6  |  HT4_HT6_Int: SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_5HT6  |  HT4_HT6_Cov: SOWS ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid + log_MME + DOU  |  HT4_HT6_Cov_noMME: SOWS ~ log_ROE + R_5HT4 + R_5HT6 + sex_female + MQS_nonopioid + DOU</t>
+    <t>HT4: SOWS ~ log_ROE + R_5HT4  |  HT6: SOWS ~ log_ROE + R_5HT6  |  HT4_HT6: SOWS ~ log_ROE + R_5HT4 + R_5HT6  |  HT4_HT6_ROEint: SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE  |  HT4_HT6_ROEint_Cov: SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE + sex_female + log_MME + MQS_nonopioid</t>
   </si>
   <si>
     <t>note</t>
@@ -453,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/nested-regression-models/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>
@@ -796,7 +769,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1">
@@ -1291,28 +1264,28 @@
         <v>17</v>
       </c>
       <c r="F12">
-        <v>12.58434356272889</v>
+        <v>-1.482333416533229</v>
       </c>
       <c r="G12">
-        <v>7.81160244837113</v>
+        <v>7.030142795707823</v>
       </c>
       <c r="H12">
-        <v>1.610981056179192</v>
+        <v>-0.210853955546714</v>
       </c>
       <c r="I12">
-        <v>0.129492513193489</v>
+        <v>0.8362704317251559</v>
       </c>
       <c r="J12" t="s">
         <v>40</v>
       </c>
       <c r="K12">
-        <v>-4.169877379843635</v>
+        <v>-16.67003356283811</v>
       </c>
       <c r="L12">
-        <v>29.33856450530141</v>
+        <v>13.70536672977166</v>
       </c>
       <c r="M12">
-        <v>1.007537347896321E-16</v>
+        <v>5.967591709771074E-17</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1332,31 +1305,31 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>0.101808255370798</v>
+        <v>-5.052394466928963</v>
       </c>
       <c r="G13">
-        <v>2.778255544528067</v>
+        <v>2.44196910438222</v>
       </c>
       <c r="H13">
-        <v>0.03664466919586112</v>
+        <v>-2.068983779468061</v>
       </c>
       <c r="I13">
-        <v>0.971285713046649</v>
+        <v>0.05903806861744179</v>
       </c>
       <c r="J13" t="s">
         <v>41</v>
       </c>
       <c r="K13">
-        <v>-5.85695725216683</v>
+        <v>-10.32794798008683</v>
       </c>
       <c r="L13">
-        <v>6.060573762908427</v>
+        <v>0.2231590462289015</v>
       </c>
       <c r="M13">
-        <v>0.006228522567607905</v>
+        <v>-0.3091002084566637</v>
       </c>
       <c r="N13">
-        <v>1.058666812069294</v>
+        <v>1.217298576161407</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1376,31 +1349,31 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>11.4663538545184</v>
+        <v>-4.924343487416539</v>
       </c>
       <c r="G14">
-        <v>4.24468838652197</v>
+        <v>10.6953544196485</v>
       </c>
       <c r="H14">
-        <v>2.701341726503921</v>
+        <v>-0.4604189159332575</v>
       </c>
       <c r="I14">
-        <v>0.01721136656046761</v>
+        <v>0.6528224053211324</v>
       </c>
       <c r="J14" t="s">
         <v>42</v>
       </c>
       <c r="K14">
-        <v>2.362402708746778</v>
+        <v>-28.03025194538596</v>
       </c>
       <c r="L14">
-        <v>20.57030500029002</v>
+        <v>18.18156497055288</v>
       </c>
       <c r="M14">
-        <v>0.5219750845035231</v>
+        <v>-0.2241675636894552</v>
       </c>
       <c r="N14">
-        <v>1.368205454794085</v>
+        <v>12.92861246286382</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1420,31 +1393,31 @@
         <v>30</v>
       </c>
       <c r="F15">
-        <v>19.01153058644842</v>
+        <v>-100.0609193113217</v>
       </c>
       <c r="G15">
-        <v>5.913730530209106</v>
+        <v>32.70827892257289</v>
       </c>
       <c r="H15">
-        <v>3.214811782398916</v>
+        <v>-3.059192431010695</v>
       </c>
       <c r="I15">
-        <v>0.006234156828495373</v>
+        <v>0.009136921450347817</v>
       </c>
       <c r="J15" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K15">
-        <v>6.327840069322836</v>
+        <v>-170.7228599024907</v>
       </c>
       <c r="L15">
-        <v>31.69522110357401</v>
+        <v>-29.3989787201526</v>
       </c>
       <c r="M15">
-        <v>0.5689576461068466</v>
+        <v>-2.994520870362604</v>
       </c>
       <c r="N15">
-        <v>1.147782499508406</v>
+        <v>52.25812053263659</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1458,37 +1431,37 @@
         <v>39</v>
       </c>
       <c r="D16" t="s">
+        <v>43</v>
+      </c>
+      <c r="E16" t="s">
         <v>44</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16">
+        <v>-4.913881332345373</v>
+      </c>
+      <c r="G16">
+        <v>4.608590902341607</v>
+      </c>
+      <c r="H16">
+        <v>-1.066243768751236</v>
+      </c>
+      <c r="I16">
+        <v>0.305715854215183</v>
+      </c>
+      <c r="J16" t="s">
         <v>45</v>
       </c>
-      <c r="F16">
-        <v>38.43819666100358</v>
-      </c>
-      <c r="G16">
-        <v>15.34620471735963</v>
-      </c>
-      <c r="H16">
-        <v>2.504736341586938</v>
-      </c>
-      <c r="I16">
-        <v>0.02523465644896915</v>
-      </c>
-      <c r="J16" t="s">
-        <v>46</v>
-      </c>
       <c r="K16">
-        <v>5.523861073149234</v>
+        <v>-14.87013666822376</v>
       </c>
       <c r="L16">
-        <v>71.35253224885793</v>
+        <v>5.04237400353301</v>
       </c>
       <c r="M16">
-        <v>0.4848237768625329</v>
+        <v>-0.5454496427603273</v>
       </c>
       <c r="N16">
-        <v>1.372949653581145</v>
+        <v>14.27279410864606</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1496,40 +1469,43 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="s">
+      <c r="F17">
+        <v>-38.60755044683631</v>
+      </c>
+      <c r="G17">
+        <v>11.05884343924604</v>
+      </c>
+      <c r="H17">
+        <v>-3.4911019998551</v>
+      </c>
+      <c r="I17">
+        <v>0.003981408461315407</v>
+      </c>
+      <c r="J17" t="s">
         <v>48</v>
       </c>
-      <c r="D17" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
-      </c>
-      <c r="F17">
-        <v>-15.36713565096405</v>
-      </c>
-      <c r="G17">
-        <v>21.47299203311028</v>
-      </c>
-      <c r="H17">
-        <v>-0.7156494831865392</v>
-      </c>
-      <c r="I17">
-        <v>0.4905802084938859</v>
-      </c>
-      <c r="J17" t="s">
-        <v>49</v>
-      </c>
       <c r="K17">
-        <v>-63.21194346832878</v>
+        <v>-62.49872918971265</v>
       </c>
       <c r="L17">
-        <v>32.47767216640069</v>
+        <v>-14.71637170395998</v>
       </c>
       <c r="M17">
-        <v>-5.124416316667158E-17</v>
+        <v>-3.469447223425601</v>
+      </c>
+      <c r="N17">
+        <v>53.86518864767415</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1537,43 +1513,40 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18">
-        <v>-4.674976059291428</v>
+        <v>-21.5905963549131</v>
       </c>
       <c r="G18">
-        <v>4.122029452980847</v>
+        <v>13.90694141586201</v>
       </c>
       <c r="H18">
-        <v>-1.134144263794796</v>
+        <v>-1.552505019564349</v>
       </c>
       <c r="I18">
-        <v>0.2831898392741702</v>
+        <v>0.1549582120472041</v>
       </c>
       <c r="J18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K18">
-        <v>-13.85943003250978</v>
+        <v>-53.05028349142035</v>
       </c>
       <c r="L18">
-        <v>4.509477913926924</v>
+        <v>9.869090781594153</v>
       </c>
       <c r="M18">
-        <v>-0.2913396801335059</v>
-      </c>
-      <c r="N18">
-        <v>1.966766544597818</v>
+        <v>3.365732214177181E-16</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1581,43 +1554,43 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F19">
-        <v>5.143365572388134</v>
+        <v>-8.496784354487081</v>
       </c>
       <c r="G19">
-        <v>4.742282035573934</v>
+        <v>2.764703214015413</v>
       </c>
       <c r="H19">
-        <v>1.084576061441622</v>
+        <v>-3.073307945465322</v>
       </c>
       <c r="I19">
-        <v>0.3035644326958254</v>
+        <v>0.01328280045763482</v>
       </c>
       <c r="J19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K19">
-        <v>-5.423097278150699</v>
+        <v>-14.75097753308327</v>
       </c>
       <c r="L19">
-        <v>15.70982842292697</v>
+        <v>-2.242591175890896</v>
       </c>
       <c r="M19">
-        <v>0.2342206632298185</v>
+        <v>-0.5295108262810746</v>
       </c>
       <c r="N19">
-        <v>1.390018303266374</v>
+        <v>2.147524359538006</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1625,43 +1598,43 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D20" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F20">
-        <v>8.445639069436496</v>
+        <v>-9.221969692190449</v>
       </c>
       <c r="G20">
-        <v>7.482020836688804</v>
+        <v>10.22341445158379</v>
       </c>
       <c r="H20">
-        <v>1.128791172035033</v>
+        <v>-0.9020440026044134</v>
       </c>
       <c r="I20">
-        <v>0.2853374672289663</v>
+        <v>0.390535304768344</v>
       </c>
       <c r="J20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K20">
-        <v>-8.225342248160672</v>
+        <v>-32.34893992209541</v>
       </c>
       <c r="L20">
-        <v>25.11662038703366</v>
+        <v>13.90500053771451</v>
       </c>
       <c r="M20">
-        <v>0.2473959978289518</v>
+        <v>-0.4199537884660274</v>
       </c>
       <c r="N20">
-        <v>1.431687608344524</v>
+        <v>15.68007473575603</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1669,43 +1642,43 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21">
+        <v>-105.067024344566</v>
+      </c>
+      <c r="G21">
+        <v>30.94298631609719</v>
+      </c>
+      <c r="H21">
+        <v>-3.395503694157276</v>
+      </c>
+      <c r="I21">
+        <v>0.007929623247483647</v>
+      </c>
+      <c r="J21" t="s">
         <v>54</v>
       </c>
-      <c r="F21">
-        <v>-5.065853173153896</v>
-      </c>
-      <c r="G21">
-        <v>4.327128867764776</v>
-      </c>
-      <c r="H21">
-        <v>-1.17071927552061</v>
-      </c>
-      <c r="I21">
-        <v>0.2688536514436826</v>
-      </c>
-      <c r="J21" t="s">
-        <v>55</v>
-      </c>
       <c r="K21">
-        <v>-14.70729712097197</v>
+        <v>-175.0649224778921</v>
       </c>
       <c r="L21">
-        <v>4.575590774664174</v>
+        <v>-35.06912621123995</v>
       </c>
       <c r="M21">
-        <v>-0.248235932977308</v>
+        <v>-3.07770212685361</v>
       </c>
       <c r="N21">
-        <v>1.3400280580278</v>
+        <v>59.43541820810998</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1713,43 +1686,43 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C22" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D22" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F22">
-        <v>0.03980764399903376</v>
+        <v>-5.738605312160323</v>
       </c>
       <c r="G22">
-        <v>0.2026225137290071</v>
+        <v>4.235059341498127</v>
       </c>
       <c r="H22">
-        <v>0.1964620972587162</v>
+        <v>-1.35502358985372</v>
       </c>
       <c r="I22">
-        <v>0.8481836928204396</v>
+        <v>0.2084405755843053</v>
       </c>
       <c r="J22" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K22">
-        <v>-0.4116634511276892</v>
+        <v>-15.31897513640576</v>
       </c>
       <c r="L22">
-        <v>0.4912787391257566</v>
+        <v>3.841764512085114</v>
       </c>
       <c r="M22">
-        <v>0.05087046523751018</v>
+        <v>-0.6321266114176419</v>
       </c>
       <c r="N22">
-        <v>1.998315248822361</v>
+        <v>15.74399719434322</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1757,43 +1730,43 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" t="s">
+        <v>46</v>
+      </c>
+      <c r="E23" t="s">
         <v>47</v>
       </c>
-      <c r="C23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" t="s">
-        <v>59</v>
-      </c>
-      <c r="E23" t="s">
-        <v>60</v>
-      </c>
       <c r="F23">
-        <v>14.42461798683992</v>
+        <v>-38.12019753044467</v>
       </c>
       <c r="G23">
-        <v>8.853568176019911</v>
+        <v>10.44315396759282</v>
       </c>
       <c r="H23">
-        <v>1.629243453041828</v>
+        <v>-3.650257158779732</v>
       </c>
       <c r="I23">
-        <v>0.1343169279454988</v>
+        <v>0.005315401802884303</v>
       </c>
       <c r="J23" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="K23">
-        <v>-5.302361244859293</v>
+        <v>-61.74425308043927</v>
       </c>
       <c r="L23">
-        <v>34.15159721853913</v>
+        <v>-14.49614198045007</v>
       </c>
       <c r="M23">
-        <v>0.4800837086866894</v>
+        <v>-3.354093624379293</v>
       </c>
       <c r="N23">
-        <v>2.587927488729032</v>
+        <v>61.08070029911875</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1801,43 +1774,43 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E24" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F24">
-        <v>-0.2640138384169573</v>
+        <v>-1.488997816671962</v>
       </c>
       <c r="G24">
-        <v>0.3552896722686179</v>
+        <v>2.971978797020552</v>
       </c>
       <c r="H24">
-        <v>-0.7430946042736329</v>
+        <v>-0.5010122609773332</v>
       </c>
       <c r="I24">
-        <v>0.4745198626094672</v>
+        <v>0.6283864769082181</v>
       </c>
       <c r="J24" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K24">
-        <v>-1.055648560908135</v>
+        <v>-8.212080940036396</v>
       </c>
       <c r="L24">
-        <v>0.5276208840742203</v>
+        <v>5.234085306692473</v>
       </c>
       <c r="M24">
-        <v>-0.166212219781739</v>
+        <v>-0.07296357584572841</v>
       </c>
       <c r="N24">
-        <v>1.491172269254365</v>
+        <v>1.534320472076546</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1845,40 +1818,43 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C25" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="F25">
-        <v>13.40998610120111</v>
+        <v>4.825047612253553</v>
       </c>
       <c r="G25">
-        <v>11.57626658740674</v>
+        <v>5.875062760835959</v>
       </c>
       <c r="H25">
-        <v>1.158403359144232</v>
+        <v>0.8212759265174215</v>
       </c>
       <c r="I25">
-        <v>0.2692341788759304</v>
+        <v>0.4327049556905518</v>
       </c>
       <c r="J25" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K25">
-        <v>-11.81253205908876</v>
+        <v>-8.465267694060508</v>
       </c>
       <c r="L25">
-        <v>38.63250426149098</v>
+        <v>18.11536291856762</v>
       </c>
       <c r="M25">
-        <v>3.530608013464148E-17</v>
+        <v>0.1605884297521016</v>
+      </c>
+      <c r="N25">
+        <v>2.765991782932822</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1886,699 +1862,696 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+      <c r="F26">
+        <v>0.256772817269631</v>
+      </c>
+      <c r="G26">
+        <v>0.1418253699229644</v>
+      </c>
+      <c r="H26">
+        <v>1.810485792556741</v>
+      </c>
+      <c r="I26">
+        <v>0.1036550289665987</v>
+      </c>
+      <c r="J26" t="s">
         <v>65</v>
       </c>
-      <c r="C26" t="s">
-        <v>66</v>
-      </c>
-      <c r="D26" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26">
-        <v>-0.9906400658211535</v>
-      </c>
-      <c r="G26">
-        <v>3.430409080313638</v>
-      </c>
-      <c r="H26">
-        <v>-0.2887819040318598</v>
-      </c>
-      <c r="I26">
-        <v>0.7776762324465246</v>
-      </c>
-      <c r="J26" t="s">
-        <v>67</v>
-      </c>
       <c r="K26">
-        <v>-8.464859381015467</v>
+        <v>-0.06405845916810787</v>
       </c>
       <c r="L26">
-        <v>6.483579249373159</v>
+        <v>0.5776040937073699</v>
       </c>
       <c r="M26">
-        <v>-0.06060632297322673</v>
+        <v>0.3281317697467693</v>
       </c>
       <c r="N26">
-        <v>1.295591328192349</v>
+        <v>2.376330748734058</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F27">
-        <v>6.912707326349967</v>
+        <v>-8.640893037556433</v>
       </c>
       <c r="G27">
-        <v>4.408629416870142</v>
+        <v>17.71863808649316</v>
       </c>
       <c r="H27">
-        <v>1.567994647020608</v>
+        <v>-0.4876725285191839</v>
       </c>
       <c r="I27">
-        <v>0.1428612720670894</v>
+        <v>0.6333300574426376</v>
       </c>
       <c r="J27" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K27">
-        <v>-2.692871008375052</v>
+        <v>-46.64359213350035</v>
       </c>
       <c r="L27">
-        <v>16.51828566107498</v>
+        <v>29.36180605838749</v>
       </c>
       <c r="M27">
-        <v>0.314682508197476</v>
-      </c>
-      <c r="N27">
-        <v>1.184753953235081</v>
+        <v>1.755277953911828E-16</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="F28">
-        <v>12.57340998343891</v>
+        <v>-4.13101128623081</v>
       </c>
       <c r="G28">
-        <v>6.807892033689157</v>
+        <v>4.408015221678555</v>
       </c>
       <c r="H28">
-        <v>1.846887394984942</v>
+        <v>-0.9371590338242382</v>
       </c>
       <c r="I28">
-        <v>0.08955753405647532</v>
+        <v>0.3645632082863994</v>
       </c>
       <c r="J28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K28">
-        <v>-2.259712522552348</v>
+        <v>-13.58526365382602</v>
       </c>
       <c r="L28">
-        <v>27.40653248943016</v>
+        <v>5.323241081364404</v>
       </c>
       <c r="M28">
-        <v>0.3762841563536695</v>
+        <v>-0.2393123145116106</v>
       </c>
       <c r="N28">
-        <v>1.221021025201629</v>
+        <v>1.017681660032122</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B29" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E29" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="F29">
-        <v>-7.39393508145343</v>
+        <v>-2.404112353126975</v>
       </c>
       <c r="G29">
-        <v>3.900281879875874</v>
+        <v>3.327712454354308</v>
       </c>
       <c r="H29">
-        <v>-1.895743771649843</v>
+        <v>-0.7224519504325552</v>
       </c>
       <c r="I29">
-        <v>0.08232816069907063</v>
+        <v>0.4819113395122917</v>
       </c>
       <c r="J29" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K29">
-        <v>-15.8919192806456</v>
+        <v>-9.541345726444376</v>
       </c>
       <c r="L29">
-        <v>1.104049117738741</v>
+        <v>4.733121020190426</v>
       </c>
       <c r="M29">
-        <v>-0.3666138657899742</v>
+        <v>-0.1844848549087003</v>
       </c>
       <c r="N29">
-        <v>1.100096059666551</v>
+        <v>1.017681660032122</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B30" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>17</v>
       </c>
       <c r="F30">
-        <v>0.08131656556672241</v>
+        <v>-14.47883150627364</v>
       </c>
       <c r="G30">
-        <v>0.1371948090192332</v>
+        <v>16.24907052258485</v>
       </c>
       <c r="H30">
-        <v>0.5927087631669996</v>
+        <v>-0.8910559829344867</v>
       </c>
       <c r="I30">
-        <v>0.5643787978107438</v>
+        <v>0.3879565847474168</v>
       </c>
       <c r="J30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K30">
-        <v>-0.217605244488128</v>
+        <v>-49.32962165415123</v>
       </c>
       <c r="L30">
-        <v>0.3802383756215728</v>
+        <v>20.37195864160394</v>
       </c>
       <c r="M30">
-        <v>0.1216464715691114</v>
-      </c>
-      <c r="N30">
-        <v>1.23904890462093</v>
+        <v>2.031058202118579E-16</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>25</v>
       </c>
       <c r="C31" t="s">
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="D31" t="s">
-        <v>62</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="F31">
-        <v>-0.1266995646867206</v>
+        <v>-6.190469706488394</v>
       </c>
       <c r="G31">
-        <v>0.3469476372412036</v>
+        <v>4.111102094990266</v>
       </c>
       <c r="H31">
-        <v>-0.3651835351702855</v>
+        <v>-1.505793230976194</v>
       </c>
       <c r="I31">
-        <v>0.7213297699540726</v>
+        <v>0.1543464482537507</v>
       </c>
       <c r="J31" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K31">
-        <v>-0.8826335279305866</v>
+        <v>-15.00790675249451</v>
       </c>
       <c r="L31">
-        <v>0.6292343985571454</v>
+        <v>2.626967339517724</v>
       </c>
       <c r="M31">
-        <v>-0.07826259329991925</v>
+        <v>-0.3586181520035131</v>
       </c>
       <c r="N31">
-        <v>1.3510088807112</v>
+        <v>1.051471993332928</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D32" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="E32" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="F32">
-        <v>-8.640893037556433</v>
+        <v>8.76259819144661</v>
       </c>
       <c r="G32">
-        <v>17.71863808649316</v>
+        <v>4.860886675950119</v>
       </c>
       <c r="H32">
-        <v>-0.4876725285191839</v>
+        <v>1.802674856585472</v>
       </c>
       <c r="I32">
-        <v>0.6333300574426376</v>
+        <v>0.09300126144817192</v>
       </c>
       <c r="J32" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K32">
-        <v>-46.64359213350035</v>
+        <v>-1.662966842608229</v>
       </c>
       <c r="L32">
-        <v>29.36180605838749</v>
+        <v>19.18816322550145</v>
       </c>
       <c r="M32">
-        <v>1.755277953911828E-16</v>
+        <v>0.4293231716234884</v>
+      </c>
+      <c r="N32">
+        <v>1.051471993332927</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" t="s">
+        <v>17</v>
+      </c>
+      <c r="F33">
+        <v>-11.92304723989088</v>
+      </c>
+      <c r="G33">
+        <v>15.02437112496234</v>
+      </c>
+      <c r="H33">
+        <v>-0.7935804527672546</v>
+      </c>
+      <c r="I33">
+        <v>0.4416845803562492</v>
+      </c>
+      <c r="J33" t="s">
         <v>73</v>
       </c>
-      <c r="B33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C33" t="s">
-        <v>16</v>
-      </c>
-      <c r="D33" t="s">
-        <v>19</v>
-      </c>
-      <c r="E33" t="s">
-        <v>20</v>
-      </c>
-      <c r="F33">
-        <v>-4.13101128623081</v>
-      </c>
-      <c r="G33">
-        <v>4.408015221678555</v>
-      </c>
-      <c r="H33">
-        <v>-0.9371590338242382</v>
-      </c>
-      <c r="I33">
-        <v>0.3645632082863994</v>
-      </c>
-      <c r="J33" t="s">
-        <v>75</v>
-      </c>
       <c r="K33">
-        <v>-13.58526365382602</v>
+        <v>-44.38122770132414</v>
       </c>
       <c r="L33">
-        <v>5.323241081364404</v>
+        <v>20.53513322154237</v>
       </c>
       <c r="M33">
-        <v>-0.2393123145116106</v>
-      </c>
-      <c r="N33">
-        <v>1.017681660032122</v>
+        <v>1.823127616382252E-16</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C34" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E34" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F34">
-        <v>-2.404112353126975</v>
+        <v>-5.916235838781732</v>
       </c>
       <c r="G34">
-        <v>3.327712454354308</v>
+        <v>3.788379360274512</v>
       </c>
       <c r="H34">
-        <v>-0.7224519504325552</v>
+        <v>-1.561679883704422</v>
       </c>
       <c r="I34">
-        <v>0.4819113395122917</v>
+        <v>0.1423697656847663</v>
       </c>
       <c r="J34" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="K34">
-        <v>-9.541345726444376</v>
+        <v>-14.10053186750935</v>
       </c>
       <c r="L34">
-        <v>4.733121020190426</v>
+        <v>2.268060189945888</v>
       </c>
       <c r="M34">
-        <v>-0.1844848549087003</v>
+        <v>-0.342731596133502</v>
       </c>
       <c r="N34">
-        <v>1.017681660032122</v>
+        <v>1.053043406545435</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C35" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D35" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E35" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F35">
-        <v>-14.47883150627364</v>
+        <v>-5.830018699276984</v>
       </c>
       <c r="G35">
-        <v>16.24907052258485</v>
+        <v>3.111174598362492</v>
       </c>
       <c r="H35">
-        <v>-0.8910559829344867</v>
+        <v>-1.873896342026418</v>
       </c>
       <c r="I35">
-        <v>0.3879565847474168</v>
+        <v>0.08359455706660525</v>
       </c>
       <c r="J35" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="K35">
-        <v>-49.32962165415123</v>
+        <v>-12.55130278636253</v>
       </c>
       <c r="L35">
-        <v>20.37195864160394</v>
+        <v>0.8912653878085584</v>
       </c>
       <c r="M35">
-        <v>2.031058202118579E-16</v>
+        <v>-0.447379321707731</v>
+      </c>
+      <c r="N35">
+        <v>1.246185532354503</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C36" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F36">
-        <v>-6.190469706488394</v>
+        <v>12.73700927774525</v>
       </c>
       <c r="G36">
-        <v>4.111102094990266</v>
+        <v>4.953039512562779</v>
       </c>
       <c r="H36">
-        <v>-1.505793230976194</v>
+        <v>2.571554142752017</v>
       </c>
       <c r="I36">
-        <v>0.1543464482537507</v>
+        <v>0.02322532608096458</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K36">
-        <v>-15.00790675249451</v>
+        <v>2.036617960582873</v>
       </c>
       <c r="L36">
-        <v>2.626967339517724</v>
+        <v>23.43740059490762</v>
       </c>
       <c r="M36">
-        <v>-0.3586181520035131</v>
+        <v>0.6240492945867497</v>
       </c>
       <c r="N36">
-        <v>1.051471993332928</v>
+        <v>1.287562935668985</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="C37" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D37" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="E37" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F37">
-        <v>8.76259819144661</v>
+        <v>19.92231839402794</v>
       </c>
       <c r="G37">
-        <v>4.860886675950119</v>
+        <v>37.96535586202688</v>
       </c>
       <c r="H37">
-        <v>1.802674856585472</v>
+        <v>0.5247499448294211</v>
       </c>
       <c r="I37">
-        <v>0.09300126144817192</v>
+        <v>0.6101694511397391</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K37">
-        <v>-1.662966842608229</v>
+        <v>-63.63886645589132</v>
       </c>
       <c r="L37">
-        <v>19.18816322550145</v>
+        <v>103.4835032439472</v>
       </c>
       <c r="M37">
-        <v>0.4293231716234884</v>
-      </c>
-      <c r="N37">
-        <v>1.051471993332927</v>
+        <v>-3.008507290981982E-16</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B38" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D38" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F38">
-        <v>-11.92304723989088</v>
+        <v>1.840514166279744</v>
       </c>
       <c r="G38">
-        <v>15.02437112496234</v>
+        <v>9.340966392486393</v>
       </c>
       <c r="H38">
-        <v>-0.7935804527672546</v>
+        <v>0.1970368042176236</v>
       </c>
       <c r="I38">
-        <v>0.4416845803562492</v>
+        <v>0.8473921746008836</v>
       </c>
       <c r="J38" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K38">
-        <v>-44.38122770132414</v>
+        <v>-18.71881424449754</v>
       </c>
       <c r="L38">
-        <v>20.53513322154237</v>
+        <v>22.39984257705703</v>
       </c>
       <c r="M38">
-        <v>1.823127616382252E-16</v>
+        <v>0.1066222468313962</v>
+      </c>
+      <c r="N38">
+        <v>5.89942369691529</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B39" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D39" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E39" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F39">
-        <v>-5.916235838781732</v>
+        <v>-109.5825434197817</v>
       </c>
       <c r="G39">
-        <v>3.788379360274512</v>
+        <v>105.4891914942232</v>
       </c>
       <c r="H39">
-        <v>-1.561679883704422</v>
+        <v>-1.038803519750008</v>
       </c>
       <c r="I39">
-        <v>0.1423697656847663</v>
+        <v>0.3211916978874486</v>
       </c>
       <c r="J39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="K39">
-        <v>-14.10053186750935</v>
+        <v>-341.7626884486322</v>
       </c>
       <c r="L39">
-        <v>2.268060189945888</v>
+        <v>122.5976016090688</v>
       </c>
       <c r="M39">
-        <v>-0.342731596133502</v>
+        <v>-8.409057753490449</v>
       </c>
       <c r="N39">
-        <v>1.053043406545435</v>
+        <v>1320.190136266348</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C40" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F40">
-        <v>-5.830018699276984</v>
+        <v>85.56994428129636</v>
       </c>
       <c r="G40">
-        <v>3.111174598362492</v>
+        <v>100.5975119630061</v>
       </c>
       <c r="H40">
-        <v>-1.873896342026418</v>
+        <v>0.8506169050459621</v>
       </c>
       <c r="I40">
-        <v>0.08359455706660525</v>
+        <v>0.4131150611845126</v>
       </c>
       <c r="J40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="K40">
-        <v>-12.55130278636253</v>
+        <v>-135.8436866914211</v>
       </c>
       <c r="L40">
-        <v>0.8912653878085584</v>
+        <v>306.9835752540138</v>
       </c>
       <c r="M40">
-        <v>-0.447379321707731</v>
+        <v>4.192496229069475</v>
       </c>
       <c r="N40">
-        <v>1.246185532354503</v>
+        <v>489.4248092751843</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C41" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E41" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="F41">
-        <v>12.73700927774525</v>
+        <v>-25.74163023980187</v>
       </c>
       <c r="G41">
-        <v>4.953039512562779</v>
+        <v>26.14597431853477</v>
       </c>
       <c r="H41">
-        <v>2.571554142752017</v>
+        <v>-0.9845351305785432</v>
       </c>
       <c r="I41">
-        <v>0.02322532608096458</v>
+        <v>0.3460125357871188</v>
       </c>
       <c r="J41" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K41">
-        <v>2.036617960582873</v>
+        <v>-83.288531711034</v>
       </c>
       <c r="L41">
-        <v>23.43740059490762</v>
+        <v>31.80527123143026</v>
       </c>
       <c r="M41">
-        <v>0.6240492945867497</v>
+        <v>-7.843968911728504</v>
       </c>
       <c r="N41">
-        <v>1.287562935668985</v>
+        <v>1278.845061605036</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B42" t="s">
         <v>38</v>
@@ -2587,864 +2560,430 @@
         <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="F42">
-        <v>-8.268611142802973</v>
+        <v>17.639413204421</v>
       </c>
       <c r="G42">
-        <v>16.25261193661871</v>
+        <v>24.62808491406031</v>
       </c>
       <c r="H42">
-        <v>-0.5087558341421412</v>
+        <v>0.7162316219865946</v>
       </c>
       <c r="I42">
-        <v>0.6201474039172781</v>
+        <v>0.4887752483418023</v>
       </c>
       <c r="J42" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="K42">
-        <v>-43.68001054591056</v>
+        <v>-36.56663621290252</v>
       </c>
       <c r="L42">
-        <v>27.14278826030461</v>
+        <v>71.84546262174452</v>
       </c>
       <c r="M42">
-        <v>1.318964894234077E-16</v>
+        <v>3.494279595034832</v>
+      </c>
+      <c r="N42">
+        <v>479.5312997909448</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C43" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D43" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E43" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F43">
-        <v>-5.307342380635628</v>
+        <v>58.27207230034049</v>
       </c>
       <c r="G43">
-        <v>3.970562714303616</v>
+        <v>70.99207589432507</v>
       </c>
       <c r="H43">
-        <v>-1.33667259844968</v>
+        <v>0.8208250225994393</v>
       </c>
       <c r="I43">
-        <v>0.2061201537949953</v>
+        <v>0.4578467972825886</v>
       </c>
       <c r="J43" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="K43">
-        <v>-13.95845536355868</v>
+        <v>-138.8335293242886</v>
       </c>
       <c r="L43">
-        <v>3.343770602287426</v>
+        <v>255.3776739249696</v>
       </c>
       <c r="M43">
-        <v>-0.3074579808699438</v>
-      </c>
-      <c r="N43">
-        <v>1.109147684013403</v>
+        <v>-1.895552567885E-15</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C44" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E44" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F44">
-        <v>-9.099017048782436</v>
+        <v>11.4512769116182</v>
       </c>
       <c r="G44">
-        <v>5.751574334270061</v>
+        <v>16.63114540810742</v>
       </c>
       <c r="H44">
-        <v>-1.582004599082905</v>
+        <v>0.688544091860076</v>
       </c>
       <c r="I44">
-        <v>0.1396334830744252</v>
+        <v>0.5289649964478058</v>
       </c>
       <c r="J44" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="K44">
-        <v>-21.63062099907479</v>
+        <v>-34.72418535055442</v>
       </c>
       <c r="L44">
-        <v>3.432586901509922</v>
+        <v>57.62673917379082</v>
       </c>
       <c r="M44">
-        <v>-0.6982331078965838</v>
+        <v>0.5042445836243472</v>
       </c>
       <c r="N44">
-        <v>4.083695181374016</v>
+        <v>9.83669863928314</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B45" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D45" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F45">
-        <v>15.05481358663095</v>
+        <v>-112.2141626290127</v>
       </c>
       <c r="G45">
-        <v>6.094344338224511</v>
+        <v>121.9789059735026</v>
       </c>
       <c r="H45">
-        <v>2.470292578022746</v>
+        <v>-0.9199472788630264</v>
       </c>
       <c r="I45">
-        <v>0.02947768688048265</v>
+        <v>0.409658641872408</v>
       </c>
       <c r="J45" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="K45">
-        <v>1.776377954097555</v>
+        <v>-450.8818990565259</v>
       </c>
       <c r="L45">
-        <v>28.33324921916435</v>
+        <v>226.4535737985005</v>
       </c>
       <c r="M45">
-        <v>0.7376100302672617</v>
+        <v>-8.34710633651148</v>
       </c>
       <c r="N45">
-        <v>1.869066553601106</v>
+        <v>1509.998127926904</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D46" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F46">
-        <v>-11.34533814942009</v>
+        <v>209.5651615071586</v>
       </c>
       <c r="G46">
-        <v>16.63916372325728</v>
+        <v>180.4058566910084</v>
       </c>
       <c r="H46">
-        <v>-0.6818454543819541</v>
+        <v>1.161631697279613</v>
       </c>
       <c r="I46">
-        <v>0.508283529140819</v>
+        <v>0.3099771561272695</v>
       </c>
       <c r="J46" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K46">
-        <v>-47.59896154458659</v>
+        <v>-291.3217962516063</v>
       </c>
       <c r="L46">
-        <v>24.90828524574641</v>
+        <v>710.4521192659237</v>
       </c>
       <c r="M46">
-        <v>-0.2709955168244061</v>
+        <v>8.837824925902453</v>
       </c>
       <c r="N46">
-        <v>3.311465531455321</v>
+        <v>1061.657115641728</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D47" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E47" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F47">
-        <v>-13.25709589756773</v>
+        <v>-26.02837444198735</v>
       </c>
       <c r="G47">
-        <v>26.67734030180806</v>
+        <v>30.26463593960569</v>
       </c>
       <c r="H47">
-        <v>-0.4969421894231796</v>
+        <v>-0.860026021589291</v>
       </c>
       <c r="I47">
-        <v>0.640306046991868</v>
+        <v>0.4382670368147617</v>
       </c>
       <c r="J47" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="K47">
-        <v>-81.83338230048412</v>
+        <v>-110.0564747570988</v>
       </c>
       <c r="L47">
-        <v>55.31919050534867</v>
+        <v>57.99972587312409</v>
       </c>
       <c r="M47">
-        <v>1.679210576819115E-16</v>
+        <v>-7.754713634477031</v>
+      </c>
+      <c r="N47">
+        <v>1491.20977191473</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B48" t="s">
+        <v>49</v>
+      </c>
+      <c r="C48" t="s">
+        <v>50</v>
+      </c>
+      <c r="D48" t="s">
+        <v>46</v>
+      </c>
+      <c r="E48" t="s">
         <v>47</v>
       </c>
-      <c r="C48" t="s">
-        <v>48</v>
-      </c>
-      <c r="D48" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" t="s">
-        <v>20</v>
-      </c>
       <c r="F48">
-        <v>-5.351816548773419</v>
+        <v>46.56070172518571</v>
       </c>
       <c r="G48">
-        <v>5.833399057035196</v>
+        <v>43.91094237885614</v>
       </c>
       <c r="H48">
-        <v>-0.9174439287363721</v>
+        <v>1.060343941686969</v>
       </c>
       <c r="I48">
-        <v>0.4009986518671736</v>
+        <v>0.3487687982580508</v>
       </c>
       <c r="J48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="K48">
-        <v>-20.3470462048061</v>
+        <v>-75.35561930721178</v>
       </c>
       <c r="L48">
-        <v>9.64341310725926</v>
+        <v>168.4770227575832</v>
       </c>
       <c r="M48">
-        <v>-0.2356614487710338</v>
+        <v>8.06435840264141</v>
       </c>
       <c r="N48">
-        <v>1.220407120976997</v>
+        <v>1060.905052376005</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C49" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="E49" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="F49">
-        <v>-6.306329816097536</v>
+        <v>-2.037020081300921</v>
       </c>
       <c r="G49">
-        <v>3.604628566697484</v>
+        <v>4.586417068283565</v>
       </c>
       <c r="H49">
-        <v>-1.749508915942293</v>
+        <v>-0.4441419197105992</v>
       </c>
       <c r="I49">
-        <v>0.1406113117428283</v>
+        <v>0.679909710319589</v>
       </c>
       <c r="J49" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="K49">
-        <v>-15.57232253386585</v>
+        <v>-14.77095530093244</v>
       </c>
       <c r="L49">
-        <v>2.959662901670779</v>
+        <v>10.6969151383306</v>
       </c>
       <c r="M49">
-        <v>-0.4690994820512128</v>
+        <v>-0.1231835560184755</v>
       </c>
       <c r="N49">
-        <v>1.329793773930606</v>
+        <v>1.410887344908986</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D50" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="E50" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="F50">
-        <v>17.70464561562267</v>
+        <v>1.421071053092973</v>
       </c>
       <c r="G50">
-        <v>6.225061644437287</v>
+        <v>9.807449047968207</v>
       </c>
       <c r="H50">
-        <v>2.844091613364751</v>
+        <v>0.1448971130150683</v>
       </c>
       <c r="I50">
-        <v>0.03607282278892086</v>
+        <v>0.8917998945863769</v>
       </c>
       <c r="J50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K50">
-        <v>1.702615226715857</v>
+        <v>-25.80877285061511</v>
       </c>
       <c r="L50">
-        <v>33.70667600452948</v>
+        <v>28.65091495680106</v>
       </c>
       <c r="M50">
-        <v>0.7466439421548475</v>
+        <v>0.0374178159688673</v>
       </c>
       <c r="N50">
-        <v>1.274754743986664</v>
+        <v>1.223116427490704</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C51" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D51" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E51" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F51">
-        <v>-2.047015879466954</v>
+        <v>0.1701031574934647</v>
       </c>
       <c r="G51">
-        <v>4.707705642821274</v>
+        <v>0.1651513178845185</v>
       </c>
       <c r="H51">
-        <v>-0.4348224028382965</v>
+        <v>1.02998365179507</v>
       </c>
       <c r="I51">
-        <v>0.6818182867599517</v>
+        <v>0.3612204238659075</v>
       </c>
       <c r="J51" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K51">
-        <v>-14.1485584924259</v>
+        <v>-0.2884304106639713</v>
       </c>
       <c r="L51">
-        <v>10.05452673349199</v>
+        <v>0.6286367256509009</v>
       </c>
       <c r="M51">
-        <v>-0.1237880262319168</v>
+        <v>0.2599845978702918</v>
       </c>
       <c r="N51">
-        <v>1.499063955792972</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" t="s">
-        <v>73</v>
-      </c>
-      <c r="B52" t="s">
-        <v>47</v>
-      </c>
-      <c r="C52" t="s">
-        <v>48</v>
-      </c>
-      <c r="D52" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" t="s">
-        <v>57</v>
-      </c>
-      <c r="F52">
-        <v>0.1648872135501665</v>
-      </c>
-      <c r="G52">
-        <v>0.1795524936073379</v>
-      </c>
-      <c r="H52">
-        <v>0.9183231613076741</v>
-      </c>
-      <c r="I52">
-        <v>0.4005802638879883</v>
-      </c>
-      <c r="J52" t="s">
-        <v>90</v>
-      </c>
-      <c r="K52">
-        <v>-0.2966671650600617</v>
-      </c>
-      <c r="L52">
-        <v>0.6264415921603946</v>
-      </c>
-      <c r="M52">
-        <v>0.2520125818971923</v>
-      </c>
-      <c r="N52">
-        <v>1.392964602008192</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" t="s">
-        <v>73</v>
-      </c>
-      <c r="B53" t="s">
-        <v>47</v>
-      </c>
-      <c r="C53" t="s">
-        <v>48</v>
-      </c>
-      <c r="D53" t="s">
-        <v>59</v>
-      </c>
-      <c r="E53" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53">
-        <v>5.252361404796313</v>
-      </c>
-      <c r="G53">
-        <v>10.77520883378978</v>
-      </c>
-      <c r="H53">
-        <v>0.4874486876138798</v>
-      </c>
-      <c r="I53">
-        <v>0.6465598524013785</v>
-      </c>
-      <c r="J53" t="s">
-        <v>93</v>
-      </c>
-      <c r="K53">
-        <v>-22.44619469853165</v>
-      </c>
-      <c r="L53">
-        <v>32.95091750812428</v>
-      </c>
-      <c r="M53">
-        <v>0.1382984278083062</v>
-      </c>
-      <c r="N53">
-        <v>1.488892642311405</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54" t="s">
-        <v>73</v>
-      </c>
-      <c r="B54" t="s">
-        <v>47</v>
-      </c>
-      <c r="C54" t="s">
-        <v>48</v>
-      </c>
-      <c r="D54" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" t="s">
-        <v>63</v>
-      </c>
-      <c r="F54">
-        <v>-0.2648268287033724</v>
-      </c>
-      <c r="G54">
-        <v>0.5632368545811415</v>
-      </c>
-      <c r="H54">
-        <v>-0.4701873227033668</v>
-      </c>
-      <c r="I54">
-        <v>0.6580155782474177</v>
-      </c>
-      <c r="J54" t="s">
-        <v>94</v>
-      </c>
-      <c r="K54">
-        <v>-1.712673256250587</v>
-      </c>
-      <c r="L54">
-        <v>1.183019598843842</v>
-      </c>
-      <c r="M54">
-        <v>-0.1551182557378029</v>
-      </c>
-      <c r="N54">
-        <v>2.01312481825023</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55" t="s">
-        <v>73</v>
-      </c>
-      <c r="B55" t="s">
-        <v>65</v>
-      </c>
-      <c r="C55" t="s">
-        <v>66</v>
-      </c>
-      <c r="D55" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55">
-        <v>-7.529712578701576</v>
-      </c>
-      <c r="G55">
-        <v>17.91499611542089</v>
-      </c>
-      <c r="H55">
-        <v>-0.4203022166563654</v>
-      </c>
-      <c r="I55">
-        <v>0.6831532393893498</v>
-      </c>
-      <c r="J55" t="s">
-        <v>95</v>
-      </c>
-      <c r="K55">
-        <v>-47.44681145665403</v>
-      </c>
-      <c r="L55">
-        <v>32.38738629925088</v>
-      </c>
-      <c r="M55">
-        <v>1.591334856696439E-16</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56" t="s">
-        <v>73</v>
-      </c>
-      <c r="B56" t="s">
-        <v>65</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="D56" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" t="s">
-        <v>20</v>
-      </c>
-      <c r="F56">
-        <v>-5.335829070697543</v>
-      </c>
-      <c r="G56">
-        <v>4.318446273743049</v>
-      </c>
-      <c r="H56">
-        <v>-1.235590009105907</v>
-      </c>
-      <c r="I56">
-        <v>0.244850349999334</v>
-      </c>
-      <c r="J56" t="s">
-        <v>96</v>
-      </c>
-      <c r="K56">
-        <v>-14.95792699343978</v>
-      </c>
-      <c r="L56">
-        <v>4.286268852044693</v>
-      </c>
-      <c r="M56">
-        <v>-0.3091082343452162</v>
-      </c>
-      <c r="N56">
-        <v>1.215968305828457</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57" t="s">
-        <v>73</v>
-      </c>
-      <c r="B57" t="s">
-        <v>65</v>
-      </c>
-      <c r="C57" t="s">
-        <v>66</v>
-      </c>
-      <c r="D57" t="s">
-        <v>22</v>
-      </c>
-      <c r="E57" t="s">
-        <v>23</v>
-      </c>
-      <c r="F57">
-        <v>-7.113151984228089</v>
-      </c>
-      <c r="G57">
-        <v>3.515901721867255</v>
-      </c>
-      <c r="H57">
-        <v>-2.023137319222443</v>
-      </c>
-      <c r="I57">
-        <v>0.07060943925131304</v>
-      </c>
-      <c r="J57" t="s">
-        <v>97</v>
-      </c>
-      <c r="K57">
-        <v>-14.94706921048596</v>
-      </c>
-      <c r="L57">
-        <v>0.7207652420297785</v>
-      </c>
-      <c r="M57">
-        <v>-0.5458433795937254</v>
-      </c>
-      <c r="N57">
-        <v>1.414279525959972</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58" t="s">
-        <v>73</v>
-      </c>
-      <c r="B58" t="s">
-        <v>65</v>
-      </c>
-      <c r="C58" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" t="s">
-        <v>30</v>
-      </c>
-      <c r="F58">
-        <v>13.08630729526657</v>
-      </c>
-      <c r="G58">
-        <v>5.524676330753031</v>
-      </c>
-      <c r="H58">
-        <v>2.368701171220082</v>
-      </c>
-      <c r="I58">
-        <v>0.03936440323939771</v>
-      </c>
-      <c r="J58" t="s">
-        <v>98</v>
-      </c>
-      <c r="K58">
-        <v>0.7765613180667739</v>
-      </c>
-      <c r="L58">
-        <v>25.39605327246637</v>
-      </c>
-      <c r="M58">
-        <v>0.6411631379295191</v>
-      </c>
-      <c r="N58">
-        <v>1.423529344943083</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59" t="s">
-        <v>73</v>
-      </c>
-      <c r="B59" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" t="s">
-        <v>66</v>
-      </c>
-      <c r="D59" t="s">
-        <v>53</v>
-      </c>
-      <c r="E59" t="s">
-        <v>54</v>
-      </c>
-      <c r="F59">
-        <v>-2.748659685458215</v>
-      </c>
-      <c r="G59">
-        <v>4.477040655051913</v>
-      </c>
-      <c r="H59">
-        <v>-0.6139456612609974</v>
-      </c>
-      <c r="I59">
-        <v>0.5529607256700446</v>
-      </c>
-      <c r="J59" t="s">
-        <v>99</v>
-      </c>
-      <c r="K59">
-        <v>-12.72412791090145</v>
-      </c>
-      <c r="L59">
-        <v>7.226808539985025</v>
-      </c>
-      <c r="M59">
-        <v>-0.164440114993212</v>
-      </c>
-      <c r="N59">
-        <v>1.393816357015049</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" t="s">
-        <v>65</v>
-      </c>
-      <c r="C60" t="s">
-        <v>66</v>
-      </c>
-      <c r="D60" t="s">
-        <v>56</v>
-      </c>
-      <c r="E60" t="s">
-        <v>57</v>
-      </c>
-      <c r="F60">
-        <v>0.07411062656601392</v>
-      </c>
-      <c r="G60">
-        <v>0.1588633856876788</v>
-      </c>
-      <c r="H60">
-        <v>0.4665053954705047</v>
-      </c>
-      <c r="I60">
-        <v>0.6508508249999618</v>
-      </c>
-      <c r="J60" t="s">
-        <v>100</v>
-      </c>
-      <c r="K60">
-        <v>-0.2798590552427833</v>
-      </c>
-      <c r="L60">
-        <v>0.4280803083748111</v>
-      </c>
-      <c r="M60">
-        <v>0.1262722374496691</v>
-      </c>
-      <c r="N60">
-        <v>1.42348302343078</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61" t="s">
-        <v>73</v>
-      </c>
-      <c r="B61" t="s">
-        <v>65</v>
-      </c>
-      <c r="C61" t="s">
-        <v>66</v>
-      </c>
-      <c r="D61" t="s">
-        <v>62</v>
-      </c>
-      <c r="E61" t="s">
-        <v>63</v>
-      </c>
-      <c r="F61">
-        <v>-0.1575681101616133</v>
-      </c>
-      <c r="G61">
-        <v>0.3212896705319878</v>
-      </c>
-      <c r="H61">
-        <v>-0.4904238281321457</v>
-      </c>
-      <c r="I61">
-        <v>0.6344162056741092</v>
-      </c>
-      <c r="J61" t="s">
-        <v>101</v>
-      </c>
-      <c r="K61">
-        <v>-0.8734461078158046</v>
-      </c>
-      <c r="L61">
-        <v>0.5583098874925779</v>
-      </c>
-      <c r="M61">
-        <v>-0.1390117383166838</v>
-      </c>
-      <c r="N61">
-        <v>1.561024447262428</v>
+        <v>1.168597551198277</v>
       </c>
     </row>
   </sheetData>
@@ -3454,7 +2993,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1">
@@ -3465,61 +3004,61 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>118</v>
       </c>
       <c r="T1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -3530,7 +3069,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D2">
         <v>19</v>
@@ -3584,7 +3123,7 @@
         <v>16</v>
       </c>
       <c r="U2" t="s">
-        <v>40</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -3595,7 +3134,7 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D3">
         <v>19</v>
@@ -3649,7 +3188,7 @@
         <v>26</v>
       </c>
       <c r="U3" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -3660,7 +3199,7 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D4">
         <v>19</v>
@@ -3725,61 +3264,61 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="D5">
         <v>19</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>0.6179526332567679</v>
+        <v>0.7616414897378524</v>
       </c>
       <c r="G5">
-        <v>0.5087962427587015</v>
+        <v>0.6699651396370264</v>
       </c>
       <c r="H5">
-        <v>5.661167710265342</v>
+        <v>8.307938622122238</v>
       </c>
       <c r="I5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K5">
-        <v>0.006326952866261992</v>
+        <v>0.001026138512433179</v>
       </c>
       <c r="L5">
-        <v>7.251131620717094</v>
+        <v>5.943672287214397</v>
       </c>
       <c r="M5">
-        <v>6.22433567342304</v>
+        <v>4.916428546218684</v>
       </c>
       <c r="N5">
-        <v>135.4013995278055</v>
+        <v>128.4377940051361</v>
       </c>
       <c r="O5">
-        <v>141.0680334028042</v>
+        <v>135.0488668593012</v>
       </c>
       <c r="P5">
-        <v>1.372949653581145</v>
+        <v>53.86518864767415</v>
       </c>
       <c r="Q5">
-        <v>1.518343285586267</v>
+        <v>0.4080423065956054</v>
       </c>
       <c r="R5">
-        <v>0.5343825586152661</v>
+        <v>0.4966147833463947</v>
       </c>
       <c r="S5">
-        <v>0.9395677558497076</v>
+        <v>0.9904069592570045</v>
       </c>
       <c r="T5" t="s">
         <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -3787,140 +3326,140 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="D6">
         <v>18</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>0.6644866040431221</v>
+        <v>0.8755938239067155</v>
       </c>
       <c r="G6">
-        <v>0.4296272268733076</v>
+        <v>0.7650105562682403</v>
       </c>
       <c r="H6">
-        <v>2.829295606803327</v>
+        <v>7.917959403851723</v>
       </c>
       <c r="I6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>0.06644504802323903</v>
+        <v>0.002739612258786987</v>
       </c>
       <c r="L6">
-        <v>7.880461003539529</v>
+        <v>5.058204781391672</v>
       </c>
       <c r="M6">
-        <v>5.873748832650199</v>
+        <v>3.576690901552269</v>
       </c>
       <c r="N6">
-        <v>132.8195378123791</v>
+        <v>116.9615567715068</v>
       </c>
       <c r="O6">
-        <v>140.8328836334445</v>
+        <v>125.8652743504684</v>
       </c>
       <c r="P6">
-        <v>2.587927488729032</v>
+        <v>61.08070029911875</v>
       </c>
       <c r="Q6">
-        <v>0.6272241535633372</v>
+        <v>0.3419559659068085</v>
       </c>
       <c r="R6">
-        <v>0.9389568041319448</v>
+        <v>0.07299395889313315</v>
       </c>
       <c r="S6">
-        <v>0.3216061019558101</v>
+        <v>0.8527234516635921</v>
       </c>
       <c r="T6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="U6" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7">
+        <v>17</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+      <c r="F7">
+        <v>0.102943928656203</v>
+      </c>
+      <c r="G7">
+        <v>-0.02520693867862511</v>
+      </c>
+      <c r="H7">
+        <v>0.8033026291365993</v>
+      </c>
+      <c r="I7">
+        <v>2</v>
+      </c>
+      <c r="J7">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D7">
-        <v>19</v>
-      </c>
-      <c r="E7">
-        <v>6</v>
-      </c>
-      <c r="F7">
-        <v>0.5920479364388634</v>
-      </c>
-      <c r="G7">
-        <v>0.3880719046582952</v>
-      </c>
-      <c r="H7">
-        <v>2.902536789595809</v>
-      </c>
-      <c r="I7">
-        <v>6</v>
-      </c>
-      <c r="J7">
-        <v>12</v>
-      </c>
       <c r="K7">
-        <v>0.05491412871439277</v>
+        <v>0.4674521150855908</v>
       </c>
       <c r="L7">
-        <v>8.093290794829741</v>
+        <v>5.620761331100267</v>
       </c>
       <c r="M7">
-        <v>6.431895319733195</v>
+        <v>5.100757793624098</v>
       </c>
       <c r="N7">
-        <v>140.6478960212083</v>
+        <v>111.643140061992</v>
       </c>
       <c r="O7">
-        <v>148.2034078545398</v>
+        <v>114.9759934382168</v>
       </c>
       <c r="P7">
-        <v>1.3510088807112</v>
+        <v>1.017681660032122</v>
       </c>
       <c r="Q7">
-        <v>0.6383819500692353</v>
+        <v>0.1710902403015153</v>
       </c>
       <c r="R7">
-        <v>0.9971162289819873</v>
+        <v>0.7525762746427802</v>
       </c>
       <c r="S7">
-        <v>0.1442953913806091</v>
+        <v>0.7475346592387072</v>
       </c>
       <c r="T7" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
       <c r="U7" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="D8">
         <v>17</v>
@@ -3929,13 +3468,13 @@
         <v>2</v>
       </c>
       <c r="F8">
-        <v>0.102943928656203</v>
+        <v>0.2447961736457296</v>
       </c>
       <c r="G8">
-        <v>-0.02520693867862511</v>
+        <v>0.1369099127379767</v>
       </c>
       <c r="H8">
-        <v>0.8033026291365993</v>
+        <v>2.269020833477955</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -3944,362 +3483,232 @@
         <v>14</v>
       </c>
       <c r="K8">
-        <v>0.4674521150855908</v>
+        <v>0.1401035926626636</v>
       </c>
       <c r="L8">
-        <v>5.620761331100267</v>
+        <v>5.157241165495551</v>
       </c>
       <c r="M8">
-        <v>5.100757793624098</v>
+        <v>4.680120097423008</v>
       </c>
       <c r="N8">
-        <v>111.643140061992</v>
+        <v>108.7169183580147</v>
       </c>
       <c r="O8">
-        <v>114.9759934382168</v>
+        <v>112.0497717342396</v>
       </c>
       <c r="P8">
-        <v>1.017681660032122</v>
+        <v>1.051471993332928</v>
       </c>
       <c r="Q8">
-        <v>0.1710902403015153</v>
+        <v>0.2325089459993227</v>
       </c>
       <c r="R8">
-        <v>0.7525762746427802</v>
+        <v>0.2351324715471814</v>
       </c>
       <c r="S8">
-        <v>0.7475346592387072</v>
+        <v>0.3494259505246413</v>
       </c>
       <c r="T8" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="U8" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="D9">
         <v>17</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>0.2447961736457296</v>
+        <v>0.4054048890378237</v>
       </c>
       <c r="G9">
-        <v>0.1369099127379767</v>
+        <v>0.2681906326619368</v>
       </c>
       <c r="H9">
-        <v>2.269020833477955</v>
+        <v>2.954539125491825</v>
       </c>
       <c r="I9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K9">
-        <v>0.1401035926626636</v>
+        <v>0.07192625518027804</v>
       </c>
       <c r="L9">
-        <v>5.157241165495551</v>
+        <v>4.748848977038465</v>
       </c>
       <c r="M9">
-        <v>4.680120097423008</v>
+        <v>4.152747962546293</v>
       </c>
       <c r="N9">
-        <v>108.7169183580147</v>
+        <v>106.6520994708445</v>
       </c>
       <c r="O9">
-        <v>112.0497717342396</v>
+        <v>110.8181661911256</v>
       </c>
       <c r="P9">
-        <v>1.051471993332928</v>
+        <v>1.287562935668985</v>
       </c>
       <c r="Q9">
-        <v>0.2325089459993227</v>
+        <v>0.16998419064986</v>
       </c>
       <c r="R9">
-        <v>0.2351324715471814</v>
+        <v>0.485419181161329</v>
       </c>
       <c r="S9">
-        <v>0.3494259505246413</v>
+        <v>0.441916180664342</v>
       </c>
       <c r="T9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="U9" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D10">
         <v>17</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10">
-        <v>0.4054048890378237</v>
+        <v>0.4540108064342469</v>
       </c>
       <c r="G10">
-        <v>0.2681906326619368</v>
+        <v>0.2058339002679955</v>
       </c>
       <c r="H10">
-        <v>2.954539125491825</v>
+        <v>1.829383778884363</v>
       </c>
       <c r="I10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K10">
-        <v>0.07192625518027804</v>
+        <v>0.1875450637843546</v>
       </c>
       <c r="L10">
-        <v>4.748848977038465</v>
+        <v>4.947035746414233</v>
       </c>
       <c r="M10">
-        <v>4.152747962546293</v>
+        <v>3.979393904776296</v>
       </c>
       <c r="N10">
-        <v>106.6520994708445</v>
+        <v>109.2023138928602</v>
       </c>
       <c r="O10">
-        <v>110.8181661911256</v>
+        <v>115.0348073012537</v>
       </c>
       <c r="P10">
-        <v>1.287562935668985</v>
+        <v>1320.190136266348</v>
       </c>
       <c r="Q10">
-        <v>0.16998419064986</v>
+        <v>3.253477369614969</v>
       </c>
       <c r="R10">
-        <v>0.485419181161329</v>
+        <v>0.2474317191663774</v>
       </c>
       <c r="S10">
-        <v>0.441916180664342</v>
+        <v>0.8515678506236393</v>
       </c>
       <c r="T10" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="U10" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="s">
+        <v>117</v>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>8</v>
+      </c>
+      <c r="F11">
+        <v>0.7819130913318976</v>
+      </c>
+      <c r="G11">
+        <v>0.3457392739956927</v>
+      </c>
+      <c r="H11">
+        <v>1.792663979940811</v>
+      </c>
+      <c r="I11">
+        <v>8</v>
+      </c>
+      <c r="J11">
+        <v>4</v>
+      </c>
+      <c r="K11">
+        <v>0.300125090744675</v>
+      </c>
+      <c r="L11">
+        <v>5.023044668455012</v>
+      </c>
+      <c r="M11">
+        <v>2.786283863240086</v>
+      </c>
+      <c r="N11">
+        <v>83.5348296062067</v>
+      </c>
+      <c r="O11">
+        <v>89.18432318082206</v>
+      </c>
+      <c r="P11">
+        <v>1509.998127926904</v>
+      </c>
+      <c r="Q11">
+        <v>1.924349946524215</v>
+      </c>
+      <c r="R11">
+        <v>0.940701540822442</v>
+      </c>
+      <c r="S11">
+        <v>0.3620081673245211</v>
+      </c>
+      <c r="T11" t="s">
+        <v>50</v>
+      </c>
+      <c r="U11" t="s">
         <v>123</v>
-      </c>
-      <c r="D11">
-        <v>17</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>0.4275819491465098</v>
-      </c>
-      <c r="G11">
-        <v>0.2367759321953464</v>
-      </c>
-      <c r="H11">
-        <v>2.240924872175016</v>
-      </c>
-      <c r="I11">
-        <v>4</v>
-      </c>
-      <c r="J11">
-        <v>12</v>
-      </c>
-      <c r="K11">
-        <v>0.1254294021577516</v>
-      </c>
-      <c r="L11">
-        <v>4.849705925112203</v>
-      </c>
-      <c r="M11">
-        <v>4.074567972196352</v>
-      </c>
-      <c r="N11">
-        <v>108.0059106762614</v>
-      </c>
-      <c r="O11">
-        <v>113.0051907405986</v>
-      </c>
-      <c r="P11">
-        <v>4.083695181374016</v>
-      </c>
-      <c r="Q11">
-        <v>0.4616117158808827</v>
-      </c>
-      <c r="R11">
-        <v>0.189617659012717</v>
-      </c>
-      <c r="S11">
-        <v>0.5494073899416438</v>
-      </c>
-      <c r="T11" t="s">
-        <v>39</v>
-      </c>
-      <c r="U11" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
-      <c r="A12" t="s">
-        <v>73</v>
-      </c>
-      <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D12">
-        <v>13</v>
-      </c>
-      <c r="E12">
-        <v>7</v>
-      </c>
-      <c r="F12">
-        <v>0.7296768150045539</v>
-      </c>
-      <c r="G12">
-        <v>0.3512243560109295</v>
-      </c>
-      <c r="H12">
-        <v>1.928054099436692</v>
-      </c>
-      <c r="I12">
-        <v>7</v>
-      </c>
-      <c r="J12">
-        <v>5</v>
-      </c>
-      <c r="K12">
-        <v>0.243759814838364</v>
-      </c>
-      <c r="L12">
-        <v>5.001944669414706</v>
-      </c>
-      <c r="M12">
-        <v>3.102074397503795</v>
-      </c>
-      <c r="N12">
-        <v>84.32624911621329</v>
-      </c>
-      <c r="O12">
-        <v>89.41079333336712</v>
-      </c>
-      <c r="P12">
-        <v>2.01312481825023</v>
-      </c>
-      <c r="Q12">
-        <v>6.166329155588139</v>
-      </c>
-      <c r="R12">
-        <v>0.06429460776493404</v>
-      </c>
-      <c r="S12">
-        <v>0.8929787345797167</v>
-      </c>
-      <c r="T12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U12" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>65</v>
-      </c>
-      <c r="C13" t="s">
-        <v>126</v>
-      </c>
-      <c r="D13">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>6</v>
-      </c>
-      <c r="F13">
-        <v>0.4853048005015976</v>
-      </c>
-      <c r="G13">
-        <v>0.1764876808025562</v>
-      </c>
-      <c r="H13">
-        <v>1.571495780332881</v>
-      </c>
-      <c r="I13">
-        <v>6</v>
-      </c>
-      <c r="J13">
-        <v>10</v>
-      </c>
-      <c r="K13">
-        <v>0.2513728366384805</v>
-      </c>
-      <c r="L13">
-        <v>5.037608654321196</v>
-      </c>
-      <c r="M13">
-        <v>3.863669465378873</v>
-      </c>
-      <c r="N13">
-        <v>110.1989007295332</v>
-      </c>
-      <c r="O13">
-        <v>116.8646074819829</v>
-      </c>
-      <c r="P13">
-        <v>1.561024447262428</v>
-      </c>
-      <c r="Q13">
-        <v>0.424578753865201</v>
-      </c>
-      <c r="R13">
-        <v>0.4218732248148095</v>
-      </c>
-      <c r="S13">
-        <v>0.920206804917915</v>
-      </c>
-      <c r="T13" t="s">
-        <v>66</v>
-      </c>
-      <c r="U13" t="s">
-        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4314,23 +3723,23 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="B2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
@@ -4338,34 +3747,34 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="B4" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>140</v>
+        <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B6" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="B7" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -426,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/nested-regression-models/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -426,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-size/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -426,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-size/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -426,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/strip-stats-v2/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -426,7 +426,7 @@
     <t>output_dir</t>
   </si>
   <si>
-    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/.claude/worktrees/figure-weight-middle/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
+    <t>/Users/kushagraverma/Work/Projects/Hydrocodone+Tramadol_Project/New_Outputs/multiple_regression_HT4_HT6_SOWS</t>
   </si>
 </sst>
 </file>

--- a/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
+++ b/New_Outputs/multiple_regression_HT4_HT6_SOWS/Stats_Multiple_Regression_HT4_HT6_SOWS.xlsx
@@ -72,7 +72,7 @@
     <t>(Intercept)</t>
   </si>
   <si>
-    <t>0.506</t>
+    <t>0.149</t>
   </si>
   <si>
     <t>log_ROE</t>
@@ -81,7 +81,7 @@
     <t>log10 ROE</t>
   </si>
   <si>
-    <t>0.575</t>
+    <t>0.248</t>
   </si>
   <si>
     <t>R_5HT4</t>
@@ -90,208 +90,208 @@
     <t>5HT4</t>
   </si>
   <si>
+    <t>0.051</t>
+  </si>
+  <si>
+    <t>HT6</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT6</t>
+  </si>
+  <si>
+    <t>0.089</t>
+  </si>
+  <si>
+    <t>0.382</t>
+  </si>
+  <si>
+    <t>R_5HT6</t>
+  </si>
+  <si>
+    <t>5HT6</t>
+  </si>
+  <si>
+    <t>0.031</t>
+  </si>
+  <si>
+    <t>HT4_HT6</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6</t>
+  </si>
+  <si>
+    <t>0.091</t>
+  </si>
+  <si>
+    <t>0.284</t>
+  </si>
+  <si>
+    <t>0.174</t>
+  </si>
+  <si>
+    <t>0.104</t>
+  </si>
+  <si>
+    <t>HT4_HT6_ROEint</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
+  </si>
+  <si>
+    <t>0.139</t>
+  </si>
+  <si>
+    <t>0.274</t>
+  </si>
+  <si>
+    <t>0.901</t>
+  </si>
+  <si>
+    <t>0.179</t>
+  </si>
+  <si>
+    <t>R_5HT4_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT4 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.447</t>
+  </si>
+  <si>
+    <t>R_5HT6_x_ROE</t>
+  </si>
+  <si>
+    <t>5-HT6 x log10 ROE</t>
+  </si>
+  <si>
+    <t>0.366</t>
+  </si>
+  <si>
+    <t>HT4_HT6_ROEint_Cov</t>
+  </si>
+  <si>
+    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.136</t>
+  </si>
+  <si>
+    <t>0.023</t>
+  </si>
+  <si>
+    <t>0.573</t>
+  </si>
+  <si>
+    <t>0.677</t>
+  </si>
+  <si>
+    <t>0.255</t>
+  </si>
+  <si>
+    <t>0.871</t>
+  </si>
+  <si>
+    <t>sex_female</t>
+  </si>
+  <si>
+    <t>Sex (female)</t>
+  </si>
+  <si>
+    <t>0.309</t>
+  </si>
+  <si>
+    <t>log_MME</t>
+  </si>
+  <si>
+    <t>log10 MME</t>
+  </si>
+  <si>
+    <t>0.028</t>
+  </si>
+  <si>
+    <t>MQS_nonopioid</t>
+  </si>
+  <si>
+    <t>MQS non-opioid</t>
+  </si>
+  <si>
+    <t>0.954</t>
+  </si>
+  <si>
+    <t>Tramadol group</t>
+  </si>
+  <si>
+    <t>0.079</t>
+  </si>
+  <si>
+    <t>0.598</t>
+  </si>
+  <si>
+    <t>0.281</t>
+  </si>
+  <si>
+    <t>0.112</t>
+  </si>
+  <si>
+    <t>0.819</t>
+  </si>
+  <si>
+    <t>0.605</t>
+  </si>
+  <si>
     <t>0.049</t>
   </si>
   <si>
-    <t>HT6</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT6</t>
-  </si>
-  <si>
-    <t>0.222</t>
-  </si>
-  <si>
-    <t>0.910</t>
-  </si>
-  <si>
-    <t>R_5HT6</t>
-  </si>
-  <si>
-    <t>5HT6</t>
-  </si>
-  <si>
-    <t>0.009</t>
-  </si>
-  <si>
-    <t>HT4_HT6</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6</t>
-  </si>
-  <si>
-    <t>0.261</t>
-  </si>
-  <si>
-    <t>0.740</t>
-  </si>
-  <si>
-    <t>0.141</t>
-  </si>
-  <si>
-    <t>0.027</t>
-  </si>
-  <si>
-    <t>HT4_HT6_ROEint</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6</t>
-  </si>
-  <si>
-    <t>0.836</t>
-  </si>
-  <si>
-    <t>0.059</t>
-  </si>
-  <si>
-    <t>0.653</t>
-  </si>
-  <si>
-    <t>R_5HT4_x_ROE</t>
-  </si>
-  <si>
-    <t>5-HT4 x log10 ROE</t>
-  </si>
-  <si>
-    <t>0.306</t>
-  </si>
-  <si>
-    <t>R_5HT6_x_ROE</t>
-  </si>
-  <si>
-    <t>5-HT6 x log10 ROE</t>
-  </si>
-  <si>
-    <t>0.004</t>
-  </si>
-  <si>
-    <t>HT4_HT6_ROEint_Cov</t>
-  </si>
-  <si>
-    <t>ROE + 5-HT4 + 5-HT6 + ROEx5-HT4 + ROEx5-HT6 + Sex + log MME + MQS non-opioid</t>
-  </si>
-  <si>
-    <t>0.155</t>
-  </si>
-  <si>
-    <t>0.013</t>
-  </si>
-  <si>
-    <t>0.391</t>
-  </si>
-  <si>
-    <t>0.008</t>
-  </si>
-  <si>
-    <t>0.208</t>
-  </si>
-  <si>
-    <t>0.005</t>
-  </si>
-  <si>
-    <t>sex_female</t>
-  </si>
-  <si>
-    <t>Sex (female)</t>
-  </si>
-  <si>
-    <t>0.628</t>
-  </si>
-  <si>
-    <t>log_MME</t>
-  </si>
-  <si>
-    <t>log10 MME</t>
-  </si>
-  <si>
-    <t>0.433</t>
-  </si>
-  <si>
-    <t>MQS_nonopioid</t>
-  </si>
-  <si>
-    <t>MQS non-opioid</t>
-  </si>
-  <si>
-    <t>0.104</t>
-  </si>
-  <si>
-    <t>Tramadol group</t>
-  </si>
-  <si>
-    <t>0.633</t>
-  </si>
-  <si>
-    <t>0.365</t>
-  </si>
-  <si>
-    <t>0.482</t>
-  </si>
-  <si>
-    <t>0.388</t>
-  </si>
-  <si>
-    <t>0.154</t>
-  </si>
-  <si>
-    <t>0.093</t>
-  </si>
-  <si>
-    <t>0.442</t>
-  </si>
-  <si>
-    <t>0.142</t>
-  </si>
-  <si>
-    <t>0.084</t>
-  </si>
-  <si>
-    <t>0.023</t>
-  </si>
-  <si>
-    <t>0.610</t>
-  </si>
-  <si>
-    <t>0.847</t>
-  </si>
-  <si>
-    <t>0.321</t>
-  </si>
-  <si>
-    <t>0.413</t>
-  </si>
-  <si>
-    <t>0.346</t>
-  </si>
-  <si>
-    <t>0.489</t>
-  </si>
-  <si>
-    <t>0.458</t>
-  </si>
-  <si>
-    <t>0.529</t>
-  </si>
-  <si>
-    <t>0.410</t>
-  </si>
-  <si>
-    <t>0.310</t>
-  </si>
-  <si>
-    <t>0.438</t>
-  </si>
-  <si>
-    <t>0.349</t>
-  </si>
-  <si>
-    <t>0.680</t>
-  </si>
-  <si>
-    <t>0.892</t>
-  </si>
-  <si>
-    <t>0.361</t>
+    <t>0.672</t>
+  </si>
+  <si>
+    <t>0.116</t>
+  </si>
+  <si>
+    <t>0.203</t>
+  </si>
+  <si>
+    <t>0.006</t>
+  </si>
+  <si>
+    <t>0.029</t>
+  </si>
+  <si>
+    <t>0.058</t>
+  </si>
+  <si>
+    <t>0.022</t>
+  </si>
+  <si>
+    <t>0.073</t>
+  </si>
+  <si>
+    <t>0.032</t>
+  </si>
+  <si>
+    <t>0.167</t>
+  </si>
+  <si>
+    <t>0.188</t>
+  </si>
+  <si>
+    <t>0.231</t>
+  </si>
+  <si>
+    <t>0.090</t>
+  </si>
+  <si>
+    <t>0.285</t>
+  </si>
+  <si>
+    <t>0.161</t>
+  </si>
+  <si>
+    <t>0.474</t>
+  </si>
+  <si>
+    <t>0.726</t>
   </si>
   <si>
     <t>formula</t>
@@ -351,43 +351,43 @@
     <t>SOWS ~ log_ROE + R_5HT4</t>
   </si>
   <si>
-    <t>0.129</t>
+    <t>0.099</t>
   </si>
   <si>
     <t>SOWS ~ log_ROE + R_5HT6</t>
   </si>
   <si>
-    <t>0.029</t>
+    <t>0.064</t>
   </si>
   <si>
     <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6</t>
   </si>
   <si>
+    <t>0.063</t>
+  </si>
+  <si>
     <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE</t>
   </si>
   <si>
-    <t>0.001</t>
+    <t>0.163</t>
   </si>
   <si>
     <t>SOWS ~ log_ROE + R_5HT4 + R_5HT6 + R_5HT4_x_ROE + R_5HT6_x_ROE +      sex_female + log_MME + MQS_nonopioid</t>
   </si>
   <si>
-    <t>0.003</t>
-  </si>
-  <si>
-    <t>0.467</t>
-  </si>
-  <si>
-    <t>0.140</t>
-  </si>
-  <si>
-    <t>0.072</t>
-  </si>
-  <si>
-    <t>0.188</t>
-  </si>
-  <si>
-    <t>0.300</t>
+    <t>0.521</t>
+  </si>
+  <si>
+    <t>0.827</t>
+  </si>
+  <si>
+    <t>0.394</t>
+  </si>
+  <si>
+    <t>0.123</t>
+  </si>
+  <si>
+    <t>0.070</t>
   </si>
   <si>
     <t>setting</t>
@@ -833,28 +833,28 @@
         <v>17</v>
       </c>
       <c r="F2">
-        <v>6.948264592497446</v>
+        <v>7.913047475757566</v>
       </c>
       <c r="G2">
-        <v>10.20597646804828</v>
+        <v>5.272141437177027</v>
       </c>
       <c r="H2">
-        <v>0.6808035090273128</v>
+        <v>1.500917145347795</v>
       </c>
       <c r="I2">
-        <v>0.5057297453432452</v>
+        <v>0.1489999842919251</v>
       </c>
       <c r="J2" t="s">
         <v>18</v>
       </c>
       <c r="K2">
-        <v>-14.68743900584551</v>
+        <v>-3.084446851009433</v>
       </c>
       <c r="L2">
-        <v>28.5839681908404</v>
+        <v>18.91054180252456</v>
       </c>
       <c r="M2">
-        <v>5.78210631170338E-17</v>
+        <v>-5.877165799787622E-17</v>
       </c>
     </row>
     <row r="3" spans="1:14">
@@ -874,31 +874,31 @@
         <v>20</v>
       </c>
       <c r="F3">
-        <v>-2.069309826956386</v>
+        <v>-1.698639833684437</v>
       </c>
       <c r="G3">
-        <v>3.616003456214789</v>
+        <v>1.426980886081605</v>
       </c>
       <c r="H3">
-        <v>-0.5722643387964367</v>
+        <v>-1.190373221009841</v>
       </c>
       <c r="I3">
-        <v>0.5750963192110992</v>
+        <v>0.247837840711889</v>
       </c>
       <c r="J3" t="s">
         <v>21</v>
       </c>
       <c r="K3">
-        <v>-9.734894715788489</v>
+        <v>-4.675269801997719</v>
       </c>
       <c r="L3">
-        <v>5.596275061875716</v>
+        <v>1.277990134628846</v>
       </c>
       <c r="M3">
-        <v>-0.1265982106227798</v>
+        <v>-0.2387339850469997</v>
       </c>
       <c r="N3">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -918,31 +918,31 @@
         <v>23</v>
       </c>
       <c r="F4">
-        <v>10.36807431222607</v>
+        <v>10.15748010733558</v>
       </c>
       <c r="G4">
-        <v>4.859666326226718</v>
+        <v>4.902195877359349</v>
       </c>
       <c r="H4">
-        <v>2.133495103618843</v>
+        <v>2.072026569612938</v>
       </c>
       <c r="I4">
-        <v>0.04871358939320595</v>
+        <v>0.05140756892357201</v>
       </c>
       <c r="J4" t="s">
         <v>24</v>
       </c>
       <c r="K4">
-        <v>0.06604191481096855</v>
+        <v>-0.06832130417343585</v>
       </c>
       <c r="L4">
-        <v>20.67010670964117</v>
+        <v>20.3832815188446</v>
       </c>
       <c r="M4">
-        <v>0.4719788464517362</v>
+        <v>0.4155529974601739</v>
       </c>
       <c r="N4">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -962,28 +962,28 @@
         <v>17</v>
       </c>
       <c r="F5">
-        <v>11.92785179923832</v>
+        <v>9.294107127314501</v>
       </c>
       <c r="G5">
-        <v>9.379602455125539</v>
+        <v>5.202436856014218</v>
       </c>
       <c r="H5">
-        <v>1.27167988795946</v>
+        <v>1.786491097257654</v>
       </c>
       <c r="I5">
-        <v>0.2216615841626851</v>
+        <v>0.08918924402800275</v>
       </c>
       <c r="J5" t="s">
         <v>27</v>
       </c>
       <c r="K5">
-        <v>-7.956017149970997</v>
+        <v>-1.557985991039905</v>
       </c>
       <c r="L5">
-        <v>31.81172074844763</v>
+        <v>20.14620024566891</v>
       </c>
       <c r="M5">
-        <v>1.031788671289922E-16</v>
+        <v>-1.828152986264443E-17</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -1003,31 +1003,31 @@
         <v>20</v>
       </c>
       <c r="F6">
-        <v>-0.3761975343543396</v>
+        <v>-1.241063306822213</v>
       </c>
       <c r="G6">
-        <v>3.28855480027763</v>
+        <v>1.387824986861629</v>
       </c>
       <c r="H6">
-        <v>-0.1143960059058708</v>
+        <v>-0.8942505853196251</v>
       </c>
       <c r="I6">
-        <v>0.9103471257583478</v>
+        <v>0.3818234823037895</v>
       </c>
       <c r="J6" t="s">
         <v>28</v>
       </c>
       <c r="K6">
-        <v>-7.347622282242381</v>
+        <v>-4.136015500617799</v>
       </c>
       <c r="L6">
-        <v>6.595227213533701</v>
+        <v>1.653888886973374</v>
       </c>
       <c r="M6">
-        <v>-0.02301537163239133</v>
+        <v>-0.1744242558415805</v>
       </c>
       <c r="N6">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -1047,31 +1047,31 @@
         <v>30</v>
       </c>
       <c r="F7">
-        <v>19.89548379935134</v>
+        <v>15.75579552233632</v>
       </c>
       <c r="G7">
-        <v>6.722708412874559</v>
+        <v>6.802518167209267</v>
       </c>
       <c r="H7">
-        <v>2.959444702562108</v>
+        <v>2.31617103182249</v>
       </c>
       <c r="I7">
-        <v>0.009227327170819108</v>
+        <v>0.03127983167990366</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
       </c>
       <c r="K7">
-        <v>5.643978609779252</v>
+        <v>1.565991276175806</v>
       </c>
       <c r="L7">
-        <v>34.14698898892342</v>
+        <v>29.94559976849683</v>
       </c>
       <c r="M7">
-        <v>0.5954116939277162</v>
+        <v>0.4517709188672954</v>
       </c>
       <c r="N7">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -1091,28 +1091,28 @@
         <v>17</v>
       </c>
       <c r="F8">
-        <v>10.55269517548552</v>
+        <v>9.059669199131973</v>
       </c>
       <c r="G8">
-        <v>9.032481823461008</v>
+        <v>5.080661597983603</v>
       </c>
       <c r="H8">
-        <v>1.168305165926368</v>
+        <v>1.783167216397082</v>
       </c>
       <c r="I8">
-        <v>0.2609176630625532</v>
+        <v>0.0905432031380675</v>
       </c>
       <c r="J8" t="s">
         <v>34</v>
       </c>
       <c r="K8">
-        <v>-8.699584102407378</v>
+        <v>-1.574277737756269</v>
       </c>
       <c r="L8">
-        <v>29.80497445337841</v>
+        <v>19.69361613602021</v>
       </c>
       <c r="M8">
-        <v>8.902323845315197E-17</v>
+        <v>-3.797115026334212E-17</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -1132,31 +1132,31 @@
         <v>20</v>
       </c>
       <c r="F9">
-        <v>-1.074469983637571</v>
+        <v>-1.507391070316635</v>
       </c>
       <c r="G9">
-        <v>3.183451650103712</v>
+        <v>1.367691041156963</v>
       </c>
       <c r="H9">
-        <v>-0.3375172930936665</v>
+        <v>-1.102142973051499</v>
       </c>
       <c r="I9">
-        <v>0.7404038177889212</v>
+        <v>0.2841653613159554</v>
       </c>
       <c r="J9" t="s">
         <v>35</v>
       </c>
       <c r="K9">
-        <v>-7.859836556562645</v>
+        <v>-4.370001318456905</v>
       </c>
       <c r="L9">
-        <v>5.710896589287503</v>
+        <v>1.355219177823634</v>
       </c>
       <c r="M9">
-        <v>-0.06573494965540054</v>
+        <v>-0.2118550796376803</v>
       </c>
       <c r="N9">
-        <v>1.028417812864244</v>
+        <v>1.020648366032284</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -1176,31 +1176,31 @@
         <v>23</v>
       </c>
       <c r="F10">
-        <v>6.94994942600395</v>
+        <v>7.081924187402105</v>
       </c>
       <c r="G10">
-        <v>4.467381285885802</v>
+        <v>5.016895869270035</v>
       </c>
       <c r="H10">
-        <v>1.555709929654213</v>
+        <v>1.41161474583935</v>
       </c>
       <c r="I10">
-        <v>0.1406203865362647</v>
+        <v>0.1742306888272678</v>
       </c>
       <c r="J10" t="s">
         <v>36</v>
       </c>
       <c r="K10">
-        <v>-2.572048385639585</v>
+        <v>-3.418559545441765</v>
       </c>
       <c r="L10">
-        <v>16.47194723764748</v>
+        <v>17.58240792024598</v>
       </c>
       <c r="M10">
-        <v>0.3163778551543743</v>
+        <v>0.2897288296666535</v>
       </c>
       <c r="N10">
-        <v>1.121305331718685</v>
+        <v>1.163657854297254</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -1220,31 +1220,31 @@
         <v>30</v>
       </c>
       <c r="F11">
-        <v>16.59536509287881</v>
+        <v>12.15238294093065</v>
       </c>
       <c r="G11">
-        <v>6.783071920019153</v>
+        <v>7.113533069894003</v>
       </c>
       <c r="H11">
-        <v>2.44658545398881</v>
+        <v>1.708347008656239</v>
       </c>
       <c r="I11">
-        <v>0.02722333562149973</v>
+        <v>0.1038582932754595</v>
       </c>
       <c r="J11" t="s">
         <v>37</v>
       </c>
       <c r="K11">
-        <v>2.137589531454713</v>
+        <v>-2.736412886186484</v>
       </c>
       <c r="L11">
-        <v>31.0531406543029</v>
+        <v>27.04117876804779</v>
       </c>
       <c r="M11">
-        <v>0.4966491159979741</v>
+        <v>0.3484491278062357</v>
       </c>
       <c r="N11">
-        <v>1.117242722797308</v>
+        <v>1.149213804608694</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -1264,28 +1264,28 @@
         <v>17</v>
       </c>
       <c r="F12">
-        <v>-1.482333416533229</v>
+        <v>8.761377903329986</v>
       </c>
       <c r="G12">
-        <v>7.030142795707823</v>
+        <v>5.647248561484908</v>
       </c>
       <c r="H12">
-        <v>-0.210853955546714</v>
+        <v>1.551441876152559</v>
       </c>
       <c r="I12">
-        <v>0.8362704317251559</v>
+        <v>0.139212331307387</v>
       </c>
       <c r="J12" t="s">
         <v>40</v>
       </c>
       <c r="K12">
-        <v>-16.67003356283811</v>
+        <v>-3.153275083587657</v>
       </c>
       <c r="L12">
-        <v>13.70536672977166</v>
+        <v>20.67603089024763</v>
       </c>
       <c r="M12">
-        <v>5.967591709771074E-17</v>
+        <v>-7.607143668028029E-17</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -1305,31 +1305,31 @@
         <v>20</v>
       </c>
       <c r="F13">
-        <v>-5.052394466928963</v>
+        <v>-1.827901194279784</v>
       </c>
       <c r="G13">
-        <v>2.44196910438222</v>
+        <v>1.616120187501757</v>
       </c>
       <c r="H13">
-        <v>-2.068983779468061</v>
+        <v>-1.131042857094313</v>
       </c>
       <c r="I13">
-        <v>0.05903806861744179</v>
+        <v>0.2737413459180834</v>
       </c>
       <c r="J13" t="s">
         <v>41</v>
       </c>
       <c r="K13">
-        <v>-10.32794798008683</v>
+        <v>-5.237616741521891</v>
       </c>
       <c r="L13">
-        <v>0.2231590462289015</v>
+        <v>1.581814352962324</v>
       </c>
       <c r="M13">
-        <v>-0.3091002084566637</v>
+        <v>-0.256900920212172</v>
       </c>
       <c r="N13">
-        <v>1.217298576161407</v>
+        <v>1.346254426039904</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -1349,31 +1349,31 @@
         <v>23</v>
       </c>
       <c r="F14">
-        <v>-4.924343487416539</v>
+        <v>-1.596897139009883</v>
       </c>
       <c r="G14">
-        <v>10.6953544196485</v>
+        <v>12.61320362256132</v>
       </c>
       <c r="H14">
-        <v>-0.4604189159332575</v>
+        <v>-0.1266051977590771</v>
       </c>
       <c r="I14">
-        <v>0.6528224053211324</v>
+        <v>0.900738265217045</v>
       </c>
       <c r="J14" t="s">
         <v>42</v>
       </c>
       <c r="K14">
-        <v>-28.03025194538596</v>
+        <v>-28.20843062827337</v>
       </c>
       <c r="L14">
-        <v>18.18156497055288</v>
+        <v>25.0146363502536</v>
       </c>
       <c r="M14">
-        <v>-0.2241675636894552</v>
+        <v>-0.06533071054423203</v>
       </c>
       <c r="N14">
-        <v>12.92861246286382</v>
+        <v>6.948413229344522</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -1393,31 +1393,31 @@
         <v>30</v>
       </c>
       <c r="F15">
-        <v>-100.0609193113217</v>
+        <v>29.0065831079555</v>
       </c>
       <c r="G15">
-        <v>32.70827892257289</v>
+        <v>20.71170801649948</v>
       </c>
       <c r="H15">
-        <v>-3.059192431010695</v>
+        <v>1.40049208326267</v>
       </c>
       <c r="I15">
-        <v>0.009136921450347817</v>
+        <v>0.1793538500250528</v>
       </c>
       <c r="J15" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="K15">
-        <v>-170.7228599024907</v>
+        <v>-14.69130110879026</v>
       </c>
       <c r="L15">
-        <v>-29.3989787201526</v>
+        <v>72.70446732470126</v>
       </c>
       <c r="M15">
-        <v>-2.994520870362604</v>
+        <v>0.8317149511939382</v>
       </c>
       <c r="N15">
-        <v>52.25812053263659</v>
+        <v>9.203259078112049</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -1431,37 +1431,37 @@
         <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F16">
-        <v>-4.913881332345373</v>
+        <v>-3.783186817605324</v>
       </c>
       <c r="G16">
-        <v>4.608590902341607</v>
+        <v>4.861923016886602</v>
       </c>
       <c r="H16">
-        <v>-1.066243768751236</v>
+        <v>-0.7781256108880018</v>
       </c>
       <c r="I16">
-        <v>0.305715854215183</v>
+        <v>0.4471903205568371</v>
       </c>
       <c r="J16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16">
-        <v>-14.87013666822376</v>
+        <v>-14.04094773685903</v>
       </c>
       <c r="L16">
-        <v>5.04237400353301</v>
+        <v>6.474574101648383</v>
       </c>
       <c r="M16">
-        <v>-0.5454496427603273</v>
+        <v>-0.4769763190703235</v>
       </c>
       <c r="N16">
-        <v>14.27279410864606</v>
+        <v>9.805012756907791</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1475,37 +1475,37 @@
         <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17">
-        <v>-38.60755044683631</v>
+        <v>5.508608235037986</v>
       </c>
       <c r="G17">
-        <v>11.05884343924604</v>
+        <v>5.925007426723953</v>
       </c>
       <c r="H17">
-        <v>-3.4911019998551</v>
+        <v>0.9297217435023196</v>
       </c>
       <c r="I17">
-        <v>0.003981408461315407</v>
+        <v>0.3655299686534108</v>
       </c>
       <c r="J17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K17">
-        <v>-62.49872918971265</v>
+        <v>-6.9920647326423</v>
       </c>
       <c r="L17">
-        <v>-14.71637170395998</v>
+        <v>18.00928120271827</v>
       </c>
       <c r="M17">
-        <v>-3.469447223425601</v>
+        <v>0.6212310575150382</v>
       </c>
       <c r="N17">
-        <v>53.86518864767415</v>
+        <v>11.6507609133532</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1513,10 +1513,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D18" t="s">
         <v>17</v>
@@ -1525,28 +1525,28 @@
         <v>17</v>
       </c>
       <c r="F18">
-        <v>-21.5905963549131</v>
+        <v>-19.21356345567447</v>
       </c>
       <c r="G18">
-        <v>13.90694141586201</v>
+        <v>12.10093891146974</v>
       </c>
       <c r="H18">
-        <v>-1.552505019564349</v>
+        <v>-1.587774601313218</v>
       </c>
       <c r="I18">
-        <v>0.1549582120472041</v>
+        <v>0.1363522228308611</v>
       </c>
       <c r="J18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K18">
-        <v>-53.05028349142035</v>
+        <v>-45.35605259378466</v>
       </c>
       <c r="L18">
-        <v>9.869090781594153</v>
+        <v>6.928925682435725</v>
       </c>
       <c r="M18">
-        <v>3.365732214177181E-16</v>
+        <v>3.967439807852342E-17</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1554,10 +1554,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>19</v>
@@ -1566,31 +1566,31 @@
         <v>20</v>
       </c>
       <c r="F19">
-        <v>-8.496784354487081</v>
+        <v>-3.960793698704914</v>
       </c>
       <c r="G19">
-        <v>2.764703214015413</v>
+        <v>1.534581172943694</v>
       </c>
       <c r="H19">
-        <v>-3.073307945465322</v>
+        <v>-2.581025864605887</v>
       </c>
       <c r="I19">
-        <v>0.01328280045763482</v>
+        <v>0.02281221568990906</v>
       </c>
       <c r="J19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K19">
-        <v>-14.75097753308327</v>
+        <v>-7.276054765530376</v>
       </c>
       <c r="L19">
-        <v>-2.242591175890896</v>
+        <v>-0.6455326318794512</v>
       </c>
       <c r="M19">
-        <v>-0.5295108262810746</v>
+        <v>-0.5652902972896005</v>
       </c>
       <c r="N19">
-        <v>2.147524359538006</v>
+        <v>1.691081219252941</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -1610,31 +1610,31 @@
         <v>23</v>
       </c>
       <c r="F20">
-        <v>-9.221969692190449</v>
+        <v>-6.431245601199924</v>
       </c>
       <c r="G20">
-        <v>10.22341445158379</v>
+        <v>11.1240704941273</v>
       </c>
       <c r="H20">
-        <v>-0.9020440026044134</v>
+        <v>-0.5781377962855552</v>
       </c>
       <c r="I20">
-        <v>0.390535304768344</v>
+        <v>0.5730502726913272</v>
       </c>
       <c r="J20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K20">
-        <v>-32.34893992209541</v>
+        <v>-30.46333882899511</v>
       </c>
       <c r="L20">
-        <v>13.90500053771451</v>
+        <v>17.60084762659525</v>
       </c>
       <c r="M20">
-        <v>-0.4199537884660274</v>
+        <v>-0.263521555986543</v>
       </c>
       <c r="N20">
-        <v>15.68007473575603</v>
+        <v>7.324461223577913</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1642,10 +1642,10 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D21" t="s">
         <v>29</v>
@@ -1654,31 +1654,31 @@
         <v>30</v>
       </c>
       <c r="F21">
-        <v>-105.067024344566</v>
+        <v>8.107146215440649</v>
       </c>
       <c r="G21">
-        <v>30.94298631609719</v>
+        <v>19.00165363593421</v>
       </c>
       <c r="H21">
-        <v>-3.395503694157276</v>
+        <v>0.4266547728303575</v>
       </c>
       <c r="I21">
-        <v>0.007929623247483647</v>
+        <v>0.6766113844606561</v>
       </c>
       <c r="J21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K21">
-        <v>-175.0649224778921</v>
+        <v>-32.94343072059387</v>
       </c>
       <c r="L21">
-        <v>-35.06912621123995</v>
+        <v>49.15772315147517</v>
       </c>
       <c r="M21">
-        <v>-3.07770212685361</v>
+        <v>0.228978517282541</v>
       </c>
       <c r="N21">
-        <v>59.43541820810998</v>
+        <v>10.15412202891363</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1686,43 +1686,43 @@
         <v>14</v>
       </c>
       <c r="B22" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F22">
-        <v>-5.738605312160323</v>
+        <v>-5.011125572581512</v>
       </c>
       <c r="G22">
-        <v>4.235059341498127</v>
+        <v>4.208081139032959</v>
       </c>
       <c r="H22">
-        <v>-1.35502358985372</v>
+        <v>-1.190833875825193</v>
       </c>
       <c r="I22">
-        <v>0.2084405755843053</v>
+        <v>0.2550090314570946</v>
       </c>
       <c r="J22" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K22">
-        <v>-15.31897513640576</v>
+        <v>-14.10213216920056</v>
       </c>
       <c r="L22">
-        <v>3.841764512085114</v>
+        <v>4.079881024037538</v>
       </c>
       <c r="M22">
-        <v>-0.6321266114176419</v>
+        <v>-0.6361836633953967</v>
       </c>
       <c r="N22">
-        <v>15.74399719434322</v>
+        <v>10.06164015914702</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -1730,43 +1730,43 @@
         <v>14</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E23" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F23">
-        <v>-38.12019753044467</v>
+        <v>0.879304407401815</v>
       </c>
       <c r="G23">
-        <v>10.44315396759282</v>
+        <v>5.297861468655832</v>
       </c>
       <c r="H23">
-        <v>-3.650257158779732</v>
+        <v>0.1659734616701692</v>
       </c>
       <c r="I23">
-        <v>0.005315401802884303</v>
+        <v>0.8707313054619974</v>
       </c>
       <c r="J23" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K23">
-        <v>-61.74425308043927</v>
+        <v>-10.56602945576418</v>
       </c>
       <c r="L23">
-        <v>-14.49614198045007</v>
+        <v>12.32463827056781</v>
       </c>
       <c r="M23">
-        <v>-3.354093624379293</v>
+        <v>0.09923223204738962</v>
       </c>
       <c r="N23">
-        <v>61.08070029911875</v>
+        <v>12.60185079627546</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -1774,43 +1774,43 @@
         <v>14</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24">
-        <v>-1.488997816671962</v>
+        <v>-4.207657837366471</v>
       </c>
       <c r="G24">
-        <v>2.971978797020552</v>
+        <v>3.976861245754905</v>
       </c>
       <c r="H24">
-        <v>-0.5010122609773332</v>
+        <v>-1.05803486150238</v>
       </c>
       <c r="I24">
-        <v>0.6283864769082181</v>
+        <v>0.3093041700479409</v>
       </c>
       <c r="J24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K24">
-        <v>-8.212080940036396</v>
+        <v>-12.79914422379694</v>
       </c>
       <c r="L24">
-        <v>5.234085306692473</v>
+        <v>4.383828549063996</v>
       </c>
       <c r="M24">
-        <v>-0.07296357584572841</v>
+        <v>-0.1957632557179835</v>
       </c>
       <c r="N24">
-        <v>1.534320472076546</v>
+        <v>1.206892310244196</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -1818,43 +1818,43 @@
         <v>14</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F25">
-        <v>4.825047612253553</v>
+        <v>17.28858167006108</v>
       </c>
       <c r="G25">
-        <v>5.875062760835959</v>
+        <v>6.999282351566853</v>
       </c>
       <c r="H25">
-        <v>0.8212759265174215</v>
+        <v>2.470050614002001</v>
       </c>
       <c r="I25">
-        <v>0.4327049556905518</v>
+        <v>0.02813202398351494</v>
       </c>
       <c r="J25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K25">
-        <v>-8.465267694060508</v>
+        <v>2.167551460002866</v>
       </c>
       <c r="L25">
-        <v>18.11536291856762</v>
+        <v>32.40961188011929</v>
       </c>
       <c r="M25">
-        <v>0.1605884297521016</v>
+        <v>0.5636233638884935</v>
       </c>
       <c r="N25">
-        <v>2.765991782932822</v>
+        <v>1.835576070806632</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -1862,48 +1862,48 @@
         <v>14</v>
       </c>
       <c r="B26" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F26">
-        <v>0.256772817269631</v>
+        <v>0.01195776720212774</v>
       </c>
       <c r="G26">
-        <v>0.1418253699229644</v>
+        <v>0.2047552269819257</v>
       </c>
       <c r="H26">
-        <v>1.810485792556741</v>
+        <v>0.05840030253871509</v>
       </c>
       <c r="I26">
-        <v>0.1036550289665987</v>
+        <v>0.9543179326651275</v>
       </c>
       <c r="J26" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26">
-        <v>-0.06405845916810787</v>
+        <v>-0.4303890074165491</v>
       </c>
       <c r="L26">
-        <v>0.5776040937073699</v>
+        <v>0.4543045418208046</v>
       </c>
       <c r="M26">
-        <v>0.3281317697467693</v>
+        <v>0.01333485794167468</v>
       </c>
       <c r="N26">
-        <v>2.376330748734058</v>
+        <v>1.838030485108268</v>
       </c>
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
@@ -1918,33 +1918,33 @@
         <v>17</v>
       </c>
       <c r="F27">
-        <v>-8.640893037556433</v>
+        <v>10.36779300560799</v>
       </c>
       <c r="G27">
-        <v>17.71863808649316</v>
+        <v>5.55780186574362</v>
       </c>
       <c r="H27">
-        <v>-0.4876725285191839</v>
+        <v>1.86544847334546</v>
       </c>
       <c r="I27">
-        <v>0.6333300574426376</v>
+        <v>0.07850373855814327</v>
       </c>
       <c r="J27" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K27">
-        <v>-46.64359213350035</v>
+        <v>-1.308715429425551</v>
       </c>
       <c r="L27">
-        <v>29.36180605838749</v>
+        <v>22.04430144064152</v>
       </c>
       <c r="M27">
-        <v>1.755277953911828E-16</v>
+        <v>-6.288606913553774E-17</v>
       </c>
     </row>
     <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
@@ -1959,36 +1959,36 @@
         <v>20</v>
       </c>
       <c r="F28">
-        <v>-4.13101128623081</v>
+        <v>0.6518023771161108</v>
       </c>
       <c r="G28">
-        <v>4.408015221678555</v>
+        <v>1.213142574635829</v>
       </c>
       <c r="H28">
-        <v>-0.9371590338242382</v>
+        <v>0.5372842324916129</v>
       </c>
       <c r="I28">
-        <v>0.3645632082863994</v>
+        <v>0.5976512977341417</v>
       </c>
       <c r="J28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K28">
-        <v>-13.58526365382602</v>
+        <v>-1.896915595891062</v>
       </c>
       <c r="L28">
-        <v>5.323241081364404</v>
+        <v>3.200520350123283</v>
       </c>
       <c r="M28">
-        <v>-0.2393123145116106</v>
+        <v>0.1243130359834203</v>
       </c>
       <c r="N28">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
@@ -2003,36 +2003,36 @@
         <v>23</v>
       </c>
       <c r="F29">
-        <v>-2.404112353126975</v>
+        <v>-3.374154870256888</v>
       </c>
       <c r="G29">
-        <v>3.327712454354308</v>
+        <v>3.033223742053101</v>
       </c>
       <c r="H29">
-        <v>-0.7224519504325552</v>
+        <v>-1.112398938290329</v>
       </c>
       <c r="I29">
-        <v>0.4819113395122917</v>
+        <v>0.2806032261317695</v>
       </c>
       <c r="J29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K29">
-        <v>-9.541345726444376</v>
+        <v>-9.746721482918645</v>
       </c>
       <c r="L29">
-        <v>4.733121020190426</v>
+        <v>2.998411742404869</v>
       </c>
       <c r="M29">
-        <v>-0.1844848549087003</v>
+        <v>-0.2573790200436657</v>
       </c>
       <c r="N29">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B30" t="s">
         <v>25</v>
@@ -2047,33 +2047,33 @@
         <v>17</v>
       </c>
       <c r="F30">
-        <v>-14.47883150627364</v>
+        <v>9.360363324502233</v>
       </c>
       <c r="G30">
-        <v>16.24907052258485</v>
+        <v>5.605580045754861</v>
       </c>
       <c r="H30">
-        <v>-0.8910559829344867</v>
+        <v>1.669829571266383</v>
       </c>
       <c r="I30">
-        <v>0.3879565847474168</v>
+        <v>0.1122510162891246</v>
       </c>
       <c r="J30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K30">
-        <v>-49.32962165415123</v>
+        <v>-2.416523341959522</v>
       </c>
       <c r="L30">
-        <v>20.37195864160394</v>
+        <v>21.13724999096399</v>
       </c>
       <c r="M30">
-        <v>2.031058202118579E-16</v>
+        <v>-4.261597981980668E-17</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
@@ -2088,36 +2088,36 @@
         <v>20</v>
       </c>
       <c r="F31">
-        <v>-6.190469706488394</v>
+        <v>0.2888690422827283</v>
       </c>
       <c r="G31">
-        <v>4.111102094990266</v>
+        <v>1.24114521023011</v>
       </c>
       <c r="H31">
-        <v>-1.505793230976194</v>
+        <v>0.2327439528443022</v>
       </c>
       <c r="I31">
-        <v>0.1543464482537507</v>
+        <v>0.8185861822122432</v>
       </c>
       <c r="J31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K31">
-        <v>-15.00790675249451</v>
+        <v>-2.318680285029306</v>
       </c>
       <c r="L31">
-        <v>2.626967339517724</v>
+        <v>2.896418369594763</v>
       </c>
       <c r="M31">
-        <v>-0.3586181520035131</v>
+        <v>0.05509367395478525</v>
       </c>
       <c r="N31">
-        <v>1.051471993332928</v>
+        <v>1.030136629964357</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B32" t="s">
         <v>25</v>
@@ -2132,36 +2132,36 @@
         <v>30</v>
       </c>
       <c r="F32">
-        <v>8.76259819144661</v>
+        <v>2.250293322683226</v>
       </c>
       <c r="G32">
-        <v>4.860886675950119</v>
+        <v>4.275417484642439</v>
       </c>
       <c r="H32">
-        <v>1.802674856585472</v>
+        <v>0.5263330027456775</v>
       </c>
       <c r="I32">
-        <v>0.09300126144817192</v>
+        <v>0.6050823636908212</v>
       </c>
       <c r="J32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K32">
-        <v>-1.662966842608229</v>
+        <v>-6.732025502033974</v>
       </c>
       <c r="L32">
-        <v>19.18816322550145</v>
+        <v>11.23261214740043</v>
       </c>
       <c r="M32">
-        <v>0.4293231716234884</v>
+        <v>0.124590213797356</v>
       </c>
       <c r="N32">
-        <v>1.051471993332927</v>
+        <v>1.030136629964357</v>
       </c>
     </row>
     <row r="33" spans="1:14">
       <c r="A33" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -2176,33 +2176,33 @@
         <v>17</v>
       </c>
       <c r="F33">
-        <v>-11.92304723989088</v>
+        <v>11.74297345053053</v>
       </c>
       <c r="G33">
-        <v>15.02437112496234</v>
+        <v>5.542555903245797</v>
       </c>
       <c r="H33">
-        <v>-0.7935804527672546</v>
+        <v>2.118692829720253</v>
       </c>
       <c r="I33">
-        <v>0.4416845803562492</v>
+        <v>0.04914615632055604</v>
       </c>
       <c r="J33" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33">
-        <v>-44.38122770132414</v>
+        <v>0.04920266485054015</v>
       </c>
       <c r="L33">
-        <v>20.53513322154237</v>
+        <v>23.43674423621052</v>
       </c>
       <c r="M33">
-        <v>1.823127616382252E-16</v>
+        <v>-9.645685286580079E-17</v>
       </c>
     </row>
     <row r="34" spans="1:14">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
         <v>32</v>
@@ -2217,36 +2217,36 @@
         <v>20</v>
       </c>
       <c r="F34">
-        <v>-5.916235838781732</v>
+        <v>0.5145471412499306</v>
       </c>
       <c r="G34">
-        <v>3.788379360274512</v>
+        <v>1.192929467883181</v>
       </c>
       <c r="H34">
-        <v>-1.561679883704422</v>
+        <v>0.4313307325394349</v>
       </c>
       <c r="I34">
-        <v>0.1423697656847663</v>
+        <v>0.6716479331623291</v>
       </c>
       <c r="J34" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K34">
-        <v>-14.10053186750935</v>
+        <v>-2.002314033346412</v>
       </c>
       <c r="L34">
-        <v>2.268060189945888</v>
+        <v>3.031408315846274</v>
       </c>
       <c r="M34">
-        <v>-0.342731596133502</v>
+        <v>0.09813544646520071</v>
       </c>
       <c r="N34">
-        <v>1.053043406545435</v>
+        <v>1.043759348059124</v>
       </c>
     </row>
     <row r="35" spans="1:14">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
         <v>32</v>
@@ -2261,36 +2261,36 @@
         <v>23</v>
       </c>
       <c r="F35">
-        <v>-5.830018699276984</v>
+        <v>-5.740347496158797</v>
       </c>
       <c r="G35">
-        <v>3.111174598362492</v>
+        <v>3.466532140056246</v>
       </c>
       <c r="H35">
-        <v>-1.873896342026418</v>
+        <v>-1.65593372980112</v>
       </c>
       <c r="I35">
-        <v>0.08359455706660525</v>
+        <v>0.1160759440165355</v>
       </c>
       <c r="J35" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K35">
-        <v>-12.55130278636253</v>
+        <v>-13.05409100630933</v>
       </c>
       <c r="L35">
-        <v>0.8912653878085584</v>
+        <v>1.573396013991735</v>
       </c>
       <c r="M35">
-        <v>-0.447379321707731</v>
+        <v>-0.4378711322041293</v>
       </c>
       <c r="N35">
-        <v>1.246185532354503</v>
+        <v>1.409860367392662</v>
       </c>
     </row>
     <row r="36" spans="1:14">
       <c r="A36" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
         <v>32</v>
@@ -2305,36 +2305,36 @@
         <v>30</v>
       </c>
       <c r="F36">
-        <v>12.73700927774525</v>
+        <v>6.312110132970886</v>
       </c>
       <c r="G36">
-        <v>4.953039512562779</v>
+        <v>4.762648621033018</v>
       </c>
       <c r="H36">
-        <v>2.571554142752017</v>
+        <v>1.325336096619655</v>
       </c>
       <c r="I36">
-        <v>0.02322532608096458</v>
+        <v>0.2025968002784576</v>
       </c>
       <c r="J36" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K36">
-        <v>2.036617960582873</v>
+        <v>-3.736200119430937</v>
       </c>
       <c r="L36">
-        <v>23.43740059490762</v>
+        <v>16.36042038537271</v>
       </c>
       <c r="M36">
-        <v>0.6240492945867497</v>
+        <v>0.3494776183406945</v>
       </c>
       <c r="N36">
-        <v>1.287562935668985</v>
+        <v>1.402025977401938</v>
       </c>
     </row>
     <row r="37" spans="1:14">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
         <v>38</v>
@@ -2349,33 +2349,33 @@
         <v>17</v>
       </c>
       <c r="F37">
-        <v>19.92231839402794</v>
+        <v>37.44731261673719</v>
       </c>
       <c r="G37">
-        <v>37.96535586202688</v>
+        <v>11.61248949778124</v>
       </c>
       <c r="H37">
-        <v>0.5247499448294211</v>
+        <v>3.224744584173112</v>
       </c>
       <c r="I37">
-        <v>0.6101694511397391</v>
+        <v>0.005669173488970513</v>
       </c>
       <c r="J37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K37">
-        <v>-63.63886645589132</v>
+        <v>12.69587715387371</v>
       </c>
       <c r="L37">
-        <v>103.4835032439472</v>
+        <v>62.19874807960066</v>
       </c>
       <c r="M37">
-        <v>-3.008507290981982E-16</v>
+        <v>-9.60045257047037E-16</v>
       </c>
     </row>
     <row r="38" spans="1:14">
       <c r="A38" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B38" t="s">
         <v>38</v>
@@ -2390,36 +2390,36 @@
         <v>20</v>
       </c>
       <c r="F38">
-        <v>1.840514166279744</v>
+        <v>6.452259204057177</v>
       </c>
       <c r="G38">
-        <v>9.340966392486393</v>
+        <v>2.669280630372199</v>
       </c>
       <c r="H38">
-        <v>0.1970368042176236</v>
+        <v>2.417227746922019</v>
       </c>
       <c r="I38">
-        <v>0.8473921746008836</v>
+        <v>0.02883651675605427</v>
       </c>
       <c r="J38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K38">
-        <v>-18.71881424449754</v>
+        <v>0.7628222174788446</v>
       </c>
       <c r="L38">
-        <v>22.39984257705703</v>
+        <v>12.14169619063551</v>
       </c>
       <c r="M38">
-        <v>0.1066222468313962</v>
+        <v>1.230587611780725</v>
       </c>
       <c r="N38">
-        <v>5.89942369691529</v>
+        <v>6.596146876697277</v>
       </c>
     </row>
     <row r="39" spans="1:14">
       <c r="A39" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B39" t="s">
         <v>38</v>
@@ -2434,36 +2434,36 @@
         <v>23</v>
       </c>
       <c r="F39">
-        <v>-109.5825434197817</v>
+        <v>-89.54712685991548</v>
       </c>
       <c r="G39">
-        <v>105.4891914942232</v>
+        <v>43.55909123348044</v>
       </c>
       <c r="H39">
-        <v>-1.038803519750008</v>
+        <v>-2.05576205389445</v>
       </c>
       <c r="I39">
-        <v>0.3211916978874486</v>
+        <v>0.05764403752353628</v>
       </c>
       <c r="J39" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K39">
-        <v>-341.7626884486322</v>
+        <v>-182.3911320745141</v>
       </c>
       <c r="L39">
-        <v>122.5976016090688</v>
+        <v>3.296878354683173</v>
       </c>
       <c r="M39">
-        <v>-8.409057753490449</v>
+        <v>-6.830614670978669</v>
       </c>
       <c r="N39">
-        <v>1320.190136266348</v>
+        <v>280.9792596993184</v>
       </c>
     </row>
     <row r="40" spans="1:14">
       <c r="A40" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B40" t="s">
         <v>38</v>
@@ -2478,36 +2478,36 @@
         <v>30</v>
       </c>
       <c r="F40">
-        <v>85.56994428129636</v>
+        <v>99.80131460211908</v>
       </c>
       <c r="G40">
-        <v>100.5975119630061</v>
+        <v>39.15681468106622</v>
       </c>
       <c r="H40">
-        <v>0.8506169050459621</v>
+        <v>2.548759785876473</v>
       </c>
       <c r="I40">
-        <v>0.4131150611845126</v>
+        <v>0.02225261206670774</v>
       </c>
       <c r="J40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K40">
-        <v>-135.8436866914211</v>
+        <v>16.34053974459216</v>
       </c>
       <c r="L40">
-        <v>306.9835752540138</v>
+        <v>183.262089459646</v>
       </c>
       <c r="M40">
-        <v>4.192496229069475</v>
+        <v>5.525620592745105</v>
       </c>
       <c r="N40">
-        <v>489.4248092751843</v>
+        <v>119.6202462527081</v>
       </c>
     </row>
     <row r="41" spans="1:14">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B41" t="s">
         <v>38</v>
@@ -2516,42 +2516,42 @@
         <v>39</v>
       </c>
       <c r="D41" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F41">
-        <v>-25.74163023980187</v>
+        <v>-20.63969212488394</v>
       </c>
       <c r="G41">
-        <v>26.14597431853477</v>
+        <v>10.70508694606517</v>
       </c>
       <c r="H41">
-        <v>-0.9845351305785432</v>
+        <v>-1.928026575484321</v>
       </c>
       <c r="I41">
-        <v>0.3460125357871188</v>
+        <v>0.07300186767836785</v>
       </c>
       <c r="J41" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K41">
-        <v>-83.288531711034</v>
+        <v>-43.45704483125243</v>
       </c>
       <c r="L41">
-        <v>31.80527123143026</v>
+        <v>2.177660581484549</v>
       </c>
       <c r="M41">
-        <v>-7.843968911728504</v>
+        <v>-6.812375590715937</v>
       </c>
       <c r="N41">
-        <v>1278.845061605036</v>
+        <v>317.7397271440617</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
         <v>38</v>
@@ -2560,48 +2560,48 @@
         <v>39</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F42">
-        <v>17.639413204421</v>
+        <v>21.72107236369533</v>
       </c>
       <c r="G42">
-        <v>24.62808491406031</v>
+        <v>9.183375500499814</v>
       </c>
       <c r="H42">
-        <v>0.7162316219865946</v>
+        <v>2.365260177209692</v>
       </c>
       <c r="I42">
-        <v>0.4887752483418023</v>
+        <v>0.03191636086786078</v>
       </c>
       <c r="J42" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K42">
-        <v>-36.56663621290252</v>
+        <v>2.147170826450232</v>
       </c>
       <c r="L42">
-        <v>71.84546262174452</v>
+        <v>41.29497390094043</v>
       </c>
       <c r="M42">
-        <v>3.494279595034832</v>
+        <v>6.226430687862629</v>
       </c>
       <c r="N42">
-        <v>479.5312997909448</v>
+        <v>176.3684335962053</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C43" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D43" t="s">
         <v>17</v>
@@ -2610,39 +2610,39 @@
         <v>17</v>
       </c>
       <c r="F43">
-        <v>58.27207230034049</v>
+        <v>28.15225871730771</v>
       </c>
       <c r="G43">
-        <v>70.99207589432507</v>
+        <v>18.5065306512548</v>
       </c>
       <c r="H43">
-        <v>0.8208250225994393</v>
+        <v>1.521206716041016</v>
       </c>
       <c r="I43">
-        <v>0.4578467972825886</v>
+        <v>0.1667010782312197</v>
       </c>
       <c r="J43" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K43">
-        <v>-138.8335293242886</v>
+        <v>-14.52387749276849</v>
       </c>
       <c r="L43">
-        <v>255.3776739249696</v>
+        <v>70.82839492738391</v>
       </c>
       <c r="M43">
-        <v>-1.895552567885E-15</v>
+        <v>5.366409050630977E-16</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C44" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D44" t="s">
         <v>19</v>
@@ -2651,42 +2651,42 @@
         <v>20</v>
       </c>
       <c r="F44">
-        <v>11.4512769116182</v>
+        <v>4.695947982353012</v>
       </c>
       <c r="G44">
-        <v>16.63114540810742</v>
+        <v>3.265298819840371</v>
       </c>
       <c r="H44">
-        <v>0.688544091860076</v>
+        <v>1.438137285880188</v>
       </c>
       <c r="I44">
-        <v>0.5289649964478058</v>
+        <v>0.1883394811665544</v>
       </c>
       <c r="J44" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K44">
-        <v>-34.72418535055442</v>
+        <v>-2.833844598876164</v>
       </c>
       <c r="L44">
-        <v>57.62673917379082</v>
+        <v>12.22574056358219</v>
       </c>
       <c r="M44">
-        <v>0.5042445836243472</v>
+        <v>0.8733120645386625</v>
       </c>
       <c r="N44">
-        <v>9.83669863928314</v>
+        <v>11.84480760643306</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C45" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D45" t="s">
         <v>22</v>
@@ -2695,42 +2695,42 @@
         <v>23</v>
       </c>
       <c r="F45">
-        <v>-112.2141626290127</v>
+        <v>-57.88906962821492</v>
       </c>
       <c r="G45">
-        <v>121.9789059735026</v>
+        <v>44.62588960467168</v>
       </c>
       <c r="H45">
-        <v>-0.9199472788630264</v>
+        <v>-1.297208193294028</v>
       </c>
       <c r="I45">
-        <v>0.409658641872408</v>
+        <v>0.2307166195150185</v>
       </c>
       <c r="J45" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K45">
-        <v>-450.8818990565259</v>
+        <v>-160.7965555937524</v>
       </c>
       <c r="L45">
-        <v>226.4535737985005</v>
+        <v>45.01841633732256</v>
       </c>
       <c r="M45">
-        <v>-8.34710633651148</v>
+        <v>-4.258048635530792</v>
       </c>
       <c r="N45">
-        <v>1509.998127926904</v>
+        <v>346.0920734595073</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
         <v>29</v>
@@ -2739,251 +2739,251 @@
         <v>30</v>
       </c>
       <c r="F46">
-        <v>209.5651615071586</v>
+        <v>84.02078296868285</v>
       </c>
       <c r="G46">
-        <v>180.4058566910084</v>
+        <v>43.63994071209607</v>
       </c>
       <c r="H46">
-        <v>1.161631697279613</v>
+        <v>1.92531844905541</v>
       </c>
       <c r="I46">
-        <v>0.3099771561272695</v>
+        <v>0.09037111241254867</v>
       </c>
       <c r="J46" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K46">
-        <v>-291.3217962516063</v>
+        <v>-16.6131007734753</v>
       </c>
       <c r="L46">
-        <v>710.4521192659237</v>
+        <v>184.654666710841</v>
       </c>
       <c r="M46">
-        <v>8.837824925902453</v>
+        <v>4.197376651088311</v>
       </c>
       <c r="N46">
-        <v>1061.657115641728</v>
+        <v>152.665366063833</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E47" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F47">
-        <v>-26.02837444198735</v>
+        <v>-12.68054287602533</v>
       </c>
       <c r="G47">
-        <v>30.26463593960569</v>
+        <v>11.06924915390555</v>
       </c>
       <c r="H47">
-        <v>-0.860026021589291</v>
+        <v>-1.14556486169175</v>
       </c>
       <c r="I47">
-        <v>0.4382670368147617</v>
+        <v>0.2850857877268563</v>
       </c>
       <c r="J47" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K47">
-        <v>-110.0564747570988</v>
+        <v>-38.20627719853672</v>
       </c>
       <c r="L47">
-        <v>57.99972587312409</v>
+        <v>12.84519144648607</v>
       </c>
       <c r="M47">
-        <v>-7.754713634477031</v>
+        <v>-4.097055487138838</v>
       </c>
       <c r="N47">
-        <v>1491.20977191473</v>
+        <v>410.8602321533518</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E48" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F48">
-        <v>46.56070172518571</v>
+        <v>15.98676478013255</v>
       </c>
       <c r="G48">
-        <v>43.91094237885614</v>
+        <v>10.36169418423983</v>
       </c>
       <c r="H48">
-        <v>1.060343941686969</v>
+        <v>1.542871705714735</v>
       </c>
       <c r="I48">
-        <v>0.3487687982580508</v>
+        <v>0.1614362367959222</v>
       </c>
       <c r="J48" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K48">
-        <v>-75.35561930721178</v>
+        <v>-7.907344856445436</v>
       </c>
       <c r="L48">
-        <v>168.4770227575832</v>
+        <v>39.88087441671055</v>
       </c>
       <c r="M48">
-        <v>8.06435840264141</v>
+        <v>4.303252597549637</v>
       </c>
       <c r="N48">
-        <v>1060.905052376005</v>
+        <v>249.8755904226072</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B49" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E49" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F49">
-        <v>-2.037020081300921</v>
+        <v>-2.681723495011985</v>
       </c>
       <c r="G49">
-        <v>4.586417068283565</v>
+        <v>3.57247899460971</v>
       </c>
       <c r="H49">
-        <v>-0.4441419197105992</v>
+        <v>-0.750661795089144</v>
       </c>
       <c r="I49">
-        <v>0.679909710319589</v>
+        <v>0.4743542940634604</v>
       </c>
       <c r="J49" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K49">
-        <v>-14.77095530093244</v>
+        <v>-10.919874829512</v>
       </c>
       <c r="L49">
-        <v>10.6969151383306</v>
+        <v>5.556427839488025</v>
       </c>
       <c r="M49">
-        <v>-0.1231835560184755</v>
+        <v>-0.1801401229521769</v>
       </c>
       <c r="N49">
-        <v>1.410887344908986</v>
+        <v>1.849788466128847</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D50" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E50" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F50">
-        <v>1.421071053092973</v>
+        <v>2.390418231441233</v>
       </c>
       <c r="G50">
-        <v>9.807449047968207</v>
+        <v>6.58647861168945</v>
       </c>
       <c r="H50">
-        <v>0.1448971130150683</v>
+        <v>0.3629281095969557</v>
       </c>
       <c r="I50">
-        <v>0.8917998945863769</v>
+        <v>0.7260605959501731</v>
       </c>
       <c r="J50" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K50">
-        <v>-25.80877285061511</v>
+        <v>-12.79802868354843</v>
       </c>
       <c r="L50">
-        <v>28.65091495680106</v>
+        <v>17.57886514643089</v>
       </c>
       <c r="M50">
-        <v>0.0374178159688673</v>
+        <v>0.08758187749974225</v>
       </c>
       <c r="N50">
-        <v>1.223116427490704</v>
+        <v>1.870583384208452</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C51" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D51" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F51">
-        <v>0.1701031574934647</v>
+        <v>0.2263379830826578</v>
       </c>
       <c r="G51">
-        <v>0.1651513178845185</v>
+        <v>0.1267340930961675</v>
       </c>
       <c r="H51">
-        <v>1.02998365179507</v>
+        <v>1.785928139406888</v>
       </c>
       <c r="I51">
-        <v>0.3612204238659075</v>
+        <v>0.111933232156775</v>
       </c>
       <c r="J51" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="K51">
-        <v>-0.2884304106639713</v>
+        <v>-0.0659113596684541</v>
       </c>
       <c r="L51">
-        <v>0.6286367256509009</v>
+        <v>0.5185873258337697</v>
       </c>
       <c r="M51">
-        <v>0.2599845978702918</v>
+        <v>0.3961869879852022</v>
       </c>
       <c r="N51">
-        <v>1.168597551198277</v>
+        <v>1.5807465367321</v>
       </c>
     </row>
   </sheetData>
@@ -3072,52 +3072,52 @@
         <v>110</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E2">
         <v>2</v>
       </c>
       <c r="F2">
-        <v>0.2259729397687755</v>
+        <v>0.2065207476416936</v>
       </c>
       <c r="G2">
-        <v>0.1292195572398724</v>
+        <v>0.1271728224058629</v>
       </c>
       <c r="H2">
-        <v>2.335555965718002</v>
+        <v>2.602723978325729</v>
       </c>
       <c r="I2">
         <v>2</v>
       </c>
       <c r="J2">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K2">
-        <v>0.1288395360226313</v>
+        <v>0.09893632045448307</v>
       </c>
       <c r="L2">
-        <v>9.65448876732324</v>
+        <v>10.17827790787121</v>
       </c>
       <c r="M2">
-        <v>8.859566502802226</v>
+        <v>9.491293088696063</v>
       </c>
       <c r="N2">
-        <v>144.8165820286772</v>
+        <v>176.7884161503726</v>
       </c>
       <c r="O2">
-        <v>148.594337945343</v>
+        <v>181.3303930140892</v>
       </c>
       <c r="P2">
-        <v>1.01163910023057</v>
+        <v>1.01381011202702</v>
       </c>
       <c r="Q2">
-        <v>0.6736587626199833</v>
+        <v>0.3230713107721403</v>
       </c>
       <c r="R2">
-        <v>0.006319962917368147</v>
+        <v>0.02969406606323984</v>
       </c>
       <c r="S2">
-        <v>0.4942644054624383</v>
+        <v>0.2689319394471413</v>
       </c>
       <c r="T2" t="s">
         <v>16</v>
@@ -3137,52 +3137,52 @@
         <v>112</v>
       </c>
       <c r="D3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E3">
         <v>2</v>
       </c>
       <c r="F3">
-        <v>0.3574824576835909</v>
+        <v>0.2400357909586464</v>
       </c>
       <c r="G3">
-        <v>0.2771677648940397</v>
+        <v>0.164039370054511</v>
       </c>
       <c r="H3">
-        <v>4.451021914761019</v>
+        <v>3.158514415585917</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
       <c r="J3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K3">
-        <v>0.02904557081489217</v>
+        <v>0.06425861993628849</v>
       </c>
       <c r="L3">
-        <v>8.796171825288376</v>
+        <v>9.961003361653974</v>
       </c>
       <c r="M3">
-        <v>8.071920858200366</v>
+        <v>9.288683529640259</v>
       </c>
       <c r="N3">
-        <v>141.2785404454863</v>
+        <v>175.7958269124355</v>
       </c>
       <c r="O3">
-        <v>145.0562963621521</v>
+        <v>180.3378037761521</v>
       </c>
       <c r="P3">
-        <v>1.007973823773254</v>
+        <v>1.001226066313922</v>
       </c>
       <c r="Q3">
-        <v>1.426543968549936</v>
+        <v>0.7653117928648423</v>
       </c>
       <c r="R3">
-        <v>0.7736547348431753</v>
+        <v>0.7609678226567607</v>
       </c>
       <c r="S3">
-        <v>0.03533620798711679</v>
+        <v>0.006865165167103117</v>
       </c>
       <c r="T3" t="s">
         <v>26</v>
@@ -3202,58 +3202,58 @@
         <v>114</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>0.4467489084893331</v>
+        <v>0.3121727979233805</v>
       </c>
       <c r="G4">
-        <v>0.3360986901871996</v>
+        <v>0.2035685028586511</v>
       </c>
       <c r="H4">
-        <v>4.037487818320187</v>
+        <v>2.874405636879482</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
       <c r="J4">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K4">
-        <v>0.02732839084250086</v>
+        <v>0.06327927724330636</v>
       </c>
       <c r="L4">
-        <v>8.429983238214069</v>
+        <v>9.72264408555907</v>
       </c>
       <c r="M4">
-        <v>7.490236666026095</v>
+        <v>8.836845670444113</v>
       </c>
       <c r="N4">
-        <v>140.4364792577257</v>
+        <v>175.5019519920719</v>
       </c>
       <c r="O4">
-        <v>145.1586741535579</v>
+        <v>181.1794230717177</v>
       </c>
       <c r="P4">
-        <v>1.121305331718685</v>
+        <v>1.163657854297254</v>
       </c>
       <c r="Q4">
-        <v>1.055844207742973</v>
+        <v>0.5616719136112069</v>
       </c>
       <c r="R4">
-        <v>0.1678965432110519</v>
+        <v>0.2264481167225968</v>
       </c>
       <c r="S4">
-        <v>0.113422347962389</v>
+        <v>0.02940430302176056</v>
       </c>
       <c r="T4" t="s">
         <v>33</v>
       </c>
       <c r="U4" t="s">
-        <v>37</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -3264,61 +3264,61 @@
         <v>38</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E5">
         <v>5</v>
       </c>
       <c r="F5">
-        <v>0.7616414897378524</v>
+        <v>0.3485291705804605</v>
       </c>
       <c r="G5">
-        <v>0.6699651396370264</v>
+        <v>0.1569201031041253</v>
       </c>
       <c r="H5">
-        <v>8.307938622122238</v>
+        <v>1.818959693144511</v>
       </c>
       <c r="I5">
         <v>5</v>
       </c>
       <c r="J5">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K5">
-        <v>0.001026138512433179</v>
+        <v>0.1627171931959964</v>
       </c>
       <c r="L5">
-        <v>5.943672287214397</v>
+        <v>10.0033287392329</v>
       </c>
       <c r="M5">
-        <v>4.916428546218684</v>
+        <v>8.600131343051054</v>
       </c>
       <c r="N5">
-        <v>128.4377940051361</v>
+        <v>178.2529364045842</v>
       </c>
       <c r="O5">
-        <v>135.0488668593012</v>
+        <v>186.2013959160882</v>
       </c>
       <c r="P5">
-        <v>53.86518864767415</v>
+        <v>11.6507609133532</v>
       </c>
       <c r="Q5">
-        <v>0.4080423065956054</v>
+        <v>9.911691944368448</v>
       </c>
       <c r="R5">
-        <v>0.4966147833463947</v>
+        <v>0.2171007712042346</v>
       </c>
       <c r="S5">
-        <v>0.9904069592570045</v>
+        <v>0.06586293874047726</v>
       </c>
       <c r="T5" t="s">
         <v>39</v>
       </c>
       <c r="U5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -3326,69 +3326,69 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D6">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E6">
         <v>8</v>
       </c>
       <c r="F6">
-        <v>0.8755938239067155</v>
+        <v>0.6312455795886844</v>
       </c>
       <c r="G6">
-        <v>0.7650105562682403</v>
+        <v>0.4043197824124902</v>
       </c>
       <c r="H6">
-        <v>7.917959403851723</v>
+        <v>2.781726835131752</v>
       </c>
       <c r="I6">
         <v>8</v>
       </c>
       <c r="J6">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K6">
-        <v>0.002739612258786987</v>
+        <v>0.04914472915410636</v>
       </c>
       <c r="L6">
-        <v>5.058204781391672</v>
+        <v>8.454451966694247</v>
       </c>
       <c r="M6">
-        <v>3.576690901552269</v>
+        <v>6.498988923960764</v>
       </c>
       <c r="N6">
-        <v>116.9615567715068</v>
+        <v>164.7857465052768</v>
       </c>
       <c r="O6">
-        <v>125.8652743504684</v>
+        <v>175.69617103886</v>
       </c>
       <c r="P6">
-        <v>61.08070029911875</v>
+        <v>12.60185079627546</v>
       </c>
       <c r="Q6">
-        <v>0.3419559659068085</v>
+        <v>5.857490933803041</v>
       </c>
       <c r="R6">
-        <v>0.07299395889313315</v>
+        <v>0.07888705722244374</v>
       </c>
       <c r="S6">
-        <v>0.8527234516635921</v>
+        <v>0.215978931672661</v>
       </c>
       <c r="T6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U6" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -3397,52 +3397,52 @@
         <v>110</v>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E7">
         <v>2</v>
       </c>
       <c r="F7">
-        <v>0.102943928656203</v>
+        <v>0.06978617937270916</v>
       </c>
       <c r="G7">
-        <v>-0.02520693867862511</v>
+        <v>-0.0335709118081009</v>
       </c>
       <c r="H7">
-        <v>0.8033026291365993</v>
+        <v>0.6751948857638331</v>
       </c>
       <c r="I7">
         <v>2</v>
       </c>
       <c r="J7">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K7">
-        <v>0.4674521150855908</v>
+        <v>0.521488925057503</v>
       </c>
       <c r="L7">
-        <v>5.620761331100267</v>
+        <v>5.431941517450086</v>
       </c>
       <c r="M7">
-        <v>5.100757793624098</v>
+        <v>5.029000637644303</v>
       </c>
       <c r="N7">
-        <v>111.643140061992</v>
+        <v>135.4347123218939</v>
       </c>
       <c r="O7">
-        <v>114.9759934382168</v>
+        <v>139.6128020727876</v>
       </c>
       <c r="P7">
-        <v>1.017681660032122</v>
+        <v>1.03589293707489</v>
       </c>
       <c r="Q7">
-        <v>0.1710902403015153</v>
+        <v>0.1425115023038777</v>
       </c>
       <c r="R7">
-        <v>0.7525762746427802</v>
+        <v>0.279581081762542</v>
       </c>
       <c r="S7">
-        <v>0.7475346592387072</v>
+        <v>0.7229717498612978</v>
       </c>
       <c r="T7" t="s">
         <v>16</v>
@@ -3453,7 +3453,7 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
@@ -3462,52 +3462,52 @@
         <v>112</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E8">
         <v>2</v>
       </c>
       <c r="F8">
-        <v>0.2447961736457296</v>
+        <v>0.02090612887947434</v>
       </c>
       <c r="G8">
-        <v>0.1369099127379767</v>
+        <v>-0.08788207902280631</v>
       </c>
       <c r="H8">
-        <v>2.269020833477955</v>
+        <v>0.1921727481553271</v>
       </c>
       <c r="I8">
         <v>2</v>
       </c>
       <c r="J8">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K8">
-        <v>0.1401035926626636</v>
+        <v>0.8268352588382435</v>
       </c>
       <c r="L8">
-        <v>5.157241165495551</v>
+        <v>5.572830803162328</v>
       </c>
       <c r="M8">
-        <v>4.680120097423008</v>
+        <v>5.159438770199294</v>
       </c>
       <c r="N8">
-        <v>108.7169183580147</v>
+        <v>136.5101863353349</v>
       </c>
       <c r="O8">
-        <v>112.0497717342396</v>
+        <v>140.6882760862286</v>
       </c>
       <c r="P8">
-        <v>1.051471993332928</v>
+        <v>1.030136629964357</v>
       </c>
       <c r="Q8">
-        <v>0.2325089459993227</v>
+        <v>0.5916014377654329</v>
       </c>
       <c r="R8">
-        <v>0.2351324715471814</v>
+        <v>0.1141920040477932</v>
       </c>
       <c r="S8">
-        <v>0.3494259505246413</v>
+        <v>0.9312555027666999</v>
       </c>
       <c r="T8" t="s">
         <v>26</v>
@@ -3518,7 +3518,7 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
@@ -3527,52 +3527,52 @@
         <v>114</v>
       </c>
       <c r="D9">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E9">
         <v>3</v>
       </c>
       <c r="F9">
-        <v>0.4054048890378237</v>
+        <v>0.156899119995542</v>
       </c>
       <c r="G9">
-        <v>0.2681906326619368</v>
+        <v>0.008116611759461212</v>
       </c>
       <c r="H9">
-        <v>2.954539125491825</v>
+        <v>1.054553534926177</v>
       </c>
       <c r="I9">
         <v>3</v>
       </c>
       <c r="J9">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K9">
-        <v>0.07192625518027804</v>
+        <v>0.3941824345294428</v>
       </c>
       <c r="L9">
-        <v>4.748848977038465</v>
+        <v>5.321269501458513</v>
       </c>
       <c r="M9">
-        <v>4.152747962546293</v>
+        <v>4.787734601098107</v>
       </c>
       <c r="N9">
-        <v>106.6520994708445</v>
+        <v>135.3698273527493</v>
       </c>
       <c r="O9">
-        <v>110.8181661911256</v>
+        <v>140.5924395413664</v>
       </c>
       <c r="P9">
-        <v>1.287562935668985</v>
+        <v>1.409860367392662</v>
       </c>
       <c r="Q9">
-        <v>0.16998419064986</v>
+        <v>0.5054444370282083</v>
       </c>
       <c r="R9">
-        <v>0.485419181161329</v>
+        <v>0.1876665696721969</v>
       </c>
       <c r="S9">
-        <v>0.441916180664342</v>
+        <v>0.9642449486988439</v>
       </c>
       <c r="T9" t="s">
         <v>33</v>
@@ -3583,61 +3583,61 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
       <c r="C10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D10">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10">
-        <v>0.4540108064342469</v>
+        <v>0.4106261299209678</v>
       </c>
       <c r="G10">
-        <v>0.2058339002679955</v>
+        <v>0.214168173227957</v>
       </c>
       <c r="H10">
-        <v>1.829383778884363</v>
+        <v>2.090147616482751</v>
       </c>
       <c r="I10">
         <v>5</v>
       </c>
       <c r="J10">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K10">
-        <v>0.1875450637843546</v>
+        <v>0.1233914630003428</v>
       </c>
       <c r="L10">
-        <v>4.947035746414233</v>
+        <v>4.736415060589902</v>
       </c>
       <c r="M10">
-        <v>3.979393904776296</v>
+        <v>4.00300134061778</v>
       </c>
       <c r="N10">
-        <v>109.2023138928602</v>
+        <v>131.8512838209695</v>
       </c>
       <c r="O10">
-        <v>115.0348073012537</v>
+        <v>139.1629408850334</v>
       </c>
       <c r="P10">
-        <v>1320.190136266348</v>
+        <v>317.7397271440617</v>
       </c>
       <c r="Q10">
-        <v>3.253477369614969</v>
+        <v>1.374791999547234</v>
       </c>
       <c r="R10">
-        <v>0.2474317191663774</v>
+        <v>0.1540438018837149</v>
       </c>
       <c r="S10">
-        <v>0.8515678506236393</v>
+        <v>0.6022247407198228</v>
       </c>
       <c r="T10" t="s">
         <v>39</v>
@@ -3648,64 +3648,64 @@
     </row>
     <row r="11" spans="1:21">
       <c r="A11" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E11">
         <v>8</v>
       </c>
       <c r="F11">
-        <v>0.7819130913318976</v>
+        <v>0.7509421679509978</v>
       </c>
       <c r="G11">
-        <v>0.3457392739956927</v>
+        <v>0.5018843359019955</v>
       </c>
       <c r="H11">
-        <v>1.792663979940811</v>
+        <v>3.015131713678651</v>
       </c>
       <c r="I11">
         <v>8</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>0.300125090744675</v>
+        <v>0.06969043486424874</v>
       </c>
       <c r="L11">
-        <v>5.023044668455012</v>
+        <v>4.128657291983423</v>
       </c>
       <c r="M11">
-        <v>2.786283863240086</v>
+        <v>2.832235536453836</v>
       </c>
       <c r="N11">
-        <v>83.5348296062067</v>
+        <v>103.6401657578037</v>
       </c>
       <c r="O11">
-        <v>89.18432318082206</v>
+        <v>111.9722991983659</v>
       </c>
       <c r="P11">
-        <v>1509.998127926904</v>
+        <v>410.8602321533518</v>
       </c>
       <c r="Q11">
-        <v>1.924349946524215</v>
+        <v>3.902469830139294</v>
       </c>
       <c r="R11">
-        <v>0.940701540822442</v>
+        <v>0.07332092988675153</v>
       </c>
       <c r="S11">
-        <v>0.3620081673245211</v>
+        <v>0.7941160687866022</v>
       </c>
       <c r="T11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U11" t="s">
         <v>123</v>
